--- a/data_pipeline/data/00_incoming/contaminant_glossary.xlsx
+++ b/data_pipeline/data/00_incoming/contaminant_glossary.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\projects\red_hill_registry_projects\red_hill_contaminant_glossary_app\data_pipeline\data\00_incoming\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A8F7DE6-F37C-4A99-9C83-3B8C9FA27ACA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DAC3EED-4AB5-4183-91D2-642821ACB47B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-18678" yWindow="6288" windowWidth="23232" windowHeight="13872" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Introduction" sheetId="1" r:id="rId1"/>
@@ -447,9 +447,6 @@
     <t>MWPLVEDNUUSJAV-UHFFFAOYSA-N</t>
   </si>
   <si>
-    <t>Anthracene is a diesel-range PAH (C14) found in coal tar and produced by incomplete combustion processes. It is used in production of dyes and as a component of synthetic fibers and plastics. It occurs in tobacco smoke, vehicle emissions, and other combustion gasses, and is found in surface waters, waste waters, and lake sediments. </t>
-  </si>
-  <si>
     <t>Antimony</t>
   </si>
   <si>
@@ -507,9 +504,6 @@
     <t>Triazine</t>
   </si>
   <si>
-    <t>Atrazine is a synthetic herbicide widely used to control broadleaf weeds and grasses in agricultural crops. It enters the environment and drinking water supplies through agricultural application, runoff and leaching into groundwater and surface water. </t>
-  </si>
-  <si>
     <t>Barium</t>
   </si>
   <si>
@@ -780,9 +774,6 @@
     <t>Linear</t>
   </si>
   <si>
-    <t>Bromochloromethane is a synthetic organic compound that is primarily used as a fire-extinguishing agent, as a solvent, and as an intermediate in the manufacture of some insecticides. It is mainly found in industrial fire protection systems and equipment. </t>
-  </si>
-  <si>
     <t>Bromodichloromethane</t>
   </si>
   <si>
@@ -1251,9 +1242,6 @@
     <t>AL = 1.3</t>
   </si>
   <si>
-    <t>Copper is a chemical element and metal that is widely used in electrical wiring and plumbing. It is also used in alloys, coatings and can be released into the environment through mining, smelting and industrial processes. Copper in drinking water is most often present due to corrosion of copper piping or erosion of natural minerals. </t>
-  </si>
-  <si>
     <t>1,2-Dibromo-3-chloropropane</t>
   </si>
   <si>
@@ -1374,9 +1362,6 @@
     <t>ZPQOPVIELGIULI-UHFFFAOYSA-N</t>
   </si>
   <si>
-    <t>m-dichlorobenzene is a chlorinated hydrocarbon used mainly as a chemical intermediate in the manufacturing of herbicides, insecticides, dyes and other industrial chemicals. </t>
-  </si>
-  <si>
     <t>p-Dichlorobenzene</t>
   </si>
   <si>
@@ -1410,9 +1395,6 @@
     <t>PXBRQCKWGAHEHS-UHFFFAOYSA-N</t>
   </si>
   <si>
-    <t>Dichlorodifluoromethane is a synthetic chlorofluorocarbon compound used mainly as a refrigerant in air conditioners and refrigerators, an aerosol propellant, and a blowing agent in foam manufacturing. </t>
-  </si>
-  <si>
     <t>1,1-Dichloroethane</t>
   </si>
   <si>
@@ -1701,9 +1683,6 @@
     <t>GVEPBJHOBDJJJI-UHFFFAOYSA-N</t>
   </si>
   <si>
-    <t>Fluoranthene is a diesel range (C16) polycyclic aromatic hydrocarbon (PAH) found in fossil fuels and formed during incomplete combustion of organic materials. It is commonly found in coal, tar, creosote, asphalt, vehicle exhaust, cigarette smoke and has been used as a chemical intermediate in the production of dyes and pesticides. </t>
-  </si>
-  <si>
     <t>Fluorene</t>
   </si>
   <si>
@@ -1791,9 +1770,6 @@
     <t>ZXFXBSWRVIQKOD-UOFFAGTMSA-N</t>
   </si>
   <si>
-    <t>Heptachlor epoxide is a chlorinated organic compound formed when the pesticide heptachlor breaks down in the environment or within living organisms. It has no major commercial use of its own but is commonly found in soil, sediments, water and wildlife due to historical use of heptachlor and is highly persistent in the environment. </t>
-  </si>
-  <si>
     <t>Heterotrophic plate count</t>
   </si>
   <si>
@@ -1821,9 +1797,6 @@
     <t>A (as industrial chemical), C (as unintentional production)</t>
   </si>
   <si>
-    <t>Hexachlorobutadiene is a chlorinated organic compound commonly produced as a byproduct during the manufacture of chlorinated hydrocarbons. It has been used as an industrial solvent and is currently used in manufacture of rubber compounds and other chlorinated chemicals. </t>
-  </si>
-  <si>
     <t>gamma-BHC (Lindane)</t>
   </si>
   <si>
@@ -1893,9 +1866,6 @@
     <t>SXQBHARYMNFBPS-UHFFFAOYSA-N</t>
   </si>
   <si>
-    <t>Indeno[1,2,3-cd]pyrene is a diesel range (C22) polycyclic aromatic hydrocarbon (PAH) formed during incomplete combustion of organic materials. It is commonly found in vehicle exhaust, coal tar, soot, cigarette smoke and polluted air, water and soil. </t>
-  </si>
-  <si>
     <t>Iron</t>
   </si>
   <si>
@@ -1929,9 +1899,6 @@
     <t>HFPZCAJZSCWRBC-UHFFFAOYSA-N</t>
   </si>
   <si>
-    <t>p-isopropyltoluene is a C10 aromatic hydrocarbon found naturally in plants including cranberries, cumin and thyme. It is manufactured from petrochemical feedsticks through the alkylation of toluene with propylene. It is used as a solvent and chemical intermediate in the production of fragrances, metal polishes, thinners for lacquers/varnishes, synthetic resins, and other industrial chemicals. </t>
-  </si>
-  <si>
     <t>Lead</t>
   </si>
   <si>
@@ -2052,9 +2019,6 @@
     <t>NTIZESTWPVYFNL-UHFFFAOYSA-N</t>
   </si>
   <si>
-    <t>4-methyl-2-pentanone is an organic compound primarily used as an industrial solvent in paints, coatings, varnishes, lacquers, adhesives, inks, and resins. It is also used in the production of pharmaceuticals, rubber products, and chemical intermediates, and in extraction and cleaning processes. </t>
-  </si>
-  <si>
     <t>Methylene chloride</t>
   </si>
   <si>
@@ -2151,9 +2115,6 @@
     <t>Transition metal (group 10)</t>
   </si>
   <si>
-    <t>Nickel is a chemical element and metal primarily used in the production of stainless steel and other metal alloys. It is also used in batteries, electroplating, coins, electronics, catalysts and industrial machinery. </t>
-  </si>
-  <si>
     <t>cis-Nonachlor</t>
   </si>
   <si>
@@ -2583,9 +2544,6 @@
     <t>total petroleum hydrocarbons, diesel range, with silica gel cleanup</t>
   </si>
   <si>
-    <t>Total petroleum hydrocarbons, diesel range, silica gel cleaned up |TPH-D (SGC)</t>
-  </si>
-  <si>
     <t>TPH-G</t>
   </si>
   <si>
@@ -2727,9 +2685,6 @@
     <t>CYRMSUTZVYGINF-UHFFFAOYSA-N</t>
   </si>
   <si>
-    <t>Trichlorofluoromethane is a synthetic chlorofluorocarbon (CFC) primarily used as a refrigerant in air conditioning and refrigeration systems, as a blowing agent in the manufacture of foam insulation and packaging materials, and as a propellant in aerosol products. </t>
-  </si>
-  <si>
     <t>1,2,3-Trichloropropane</t>
   </si>
   <si>
@@ -3261,7 +3216,52 @@
     <t>contaminant_glossary</t>
   </si>
   <si>
-    <t>20260716</t>
+    <t>Total petroleum hydrocarbons, diesel range, silica gel cleaned up | TPH-D (SGC)</t>
+  </si>
+  <si>
+    <t>Anthracene is a diesel-range PAH (C14) found in coal tar and produced by incomplete combustion processes. It is used in production of dyes and as a component of synthetic fibers and plastics. It occurs in tobacco smoke, vehicle emissions, and other combustion gasses, and is found in surface waters, waste waters, and lake sediments.</t>
+  </si>
+  <si>
+    <t>Atrazine is a synthetic herbicide widely used to control broadleaf weeds and grasses in agricultural crops. It enters the environment and drinking water supplies through agricultural application, runoff and leaching into groundwater and surface water.</t>
+  </si>
+  <si>
+    <t>Bromochloromethane is a synthetic organic compound that is primarily used as a fire-extinguishing agent, as a solvent, and as an intermediate in the manufacture of some insecticides. It is mainly found in industrial fire protection systems and equipment.</t>
+  </si>
+  <si>
+    <t>Copper is a chemical element and metal that is widely used in electrical wiring and plumbing. It is also used in alloys, coatings and can be released into the environment through mining, smelting and industrial processes. Copper in drinking water is most often present due to corrosion of copper piping or erosion of natural minerals.</t>
+  </si>
+  <si>
+    <t>m-dichlorobenzene is a chlorinated hydrocarbon used mainly as a chemical intermediate in the manufacturing of herbicides, insecticides, dyes and other industrial chemicals.</t>
+  </si>
+  <si>
+    <t>Dichlorodifluoromethane is a synthetic chlorofluorocarbon compound used mainly as a refrigerant in air conditioners and refrigerators, an aerosol propellant, and a blowing agent in foam manufacturing.</t>
+  </si>
+  <si>
+    <t>Fluoranthene is a diesel range (C16) polycyclic aromatic hydrocarbon (PAH) found in fossil fuels and formed during incomplete combustion of organic materials. It is commonly found in coal, tar, creosote, asphalt, vehicle exhaust, cigarette smoke and has been used as a chemical intermediate in the production of dyes and pesticides.</t>
+  </si>
+  <si>
+    <t>Heptachlor epoxide is a chlorinated organic compound formed when the pesticide heptachlor breaks down in the environment or within living organisms. It has no major commercial use of its own but is commonly found in soil, sediments, water and wildlife due to historical use of heptachlor and is highly persistent in the environment.</t>
+  </si>
+  <si>
+    <t>Hexachlorobutadiene is a chlorinated organic compound commonly produced as a byproduct during the manufacture of chlorinated hydrocarbons. It has been used as an industrial solvent and is currently used in manufacture of rubber compounds and other chlorinated chemicals.</t>
+  </si>
+  <si>
+    <t>Indeno[1,2,3-cd]pyrene is a diesel range (C22) polycyclic aromatic hydrocarbon (PAH) formed during incomplete combustion of organic materials. It is commonly found in vehicle exhaust, coal tar, soot, cigarette smoke and polluted air, water and soil.</t>
+  </si>
+  <si>
+    <t>p-isopropyltoluene is a C10 aromatic hydrocarbon found naturally in plants including cranberries, cumin and thyme. It is manufactured from petrochemical feedsticks through the alkylation of toluene with propylene. It is used as a solvent and chemical intermediate in the production of fragrances, metal polishes, thinners for lacquers/varnishes, synthetic resins, and other industrial chemicals.</t>
+  </si>
+  <si>
+    <t>4-methyl-2-pentanone is an organic compound primarily used as an industrial solvent in paints, coatings, varnishes, lacquers, adhesives, inks, and resins. It is also used in the production of pharmaceuticals, rubber products, and chemical intermediates, and in extraction and cleaning processes.</t>
+  </si>
+  <si>
+    <t>Nickel is a chemical element and metal primarily used in the production of stainless steel and other metal alloys. It is also used in batteries, electroplating, coins, electronics, catalysts and industrial machinery.</t>
+  </si>
+  <si>
+    <t>Trichlorofluoromethane is a synthetic chlorofluorocarbon (CFC) primarily used as a refrigerant in air conditioning and refrigeration systems, as a blowing agent in the manufacture of foam insulation and packaging materials, and as a propellant in aerosol products.</t>
+  </si>
+  <si>
+    <t>20260810</t>
   </si>
 </sst>
 </file>
@@ -3663,6 +3663,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="15" xfId="1"/>
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="15" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3671,7 +3672,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="15" xfId="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4032,14 +4032,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="33"/>
+      <c r="A1" s="32" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="34"/>
       <c r="H1" s="1" t="s">
         <v>1</v>
       </c>
@@ -4048,12 +4048,12 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="34"/>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="36"/>
+      <c r="A2" s="35"/>
+      <c r="B2" s="36"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="37"/>
       <c r="H2" s="3" t="s">
         <v>3</v>
       </c>
@@ -4150,12 +4150,12 @@
     </row>
     <row r="18" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
-        <v>1055</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
-        <v>1056</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4170,7 +4170,7 @@
     </row>
     <row r="22" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C22" s="4" t="s">
-        <v>1057</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4180,7 +4180,7 @@
     </row>
     <row r="24" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B24" s="24" t="s">
-        <v>1058</v>
+        <v>1043</v>
       </c>
       <c r="C24" s="4"/>
     </row>
@@ -4196,18 +4196,18 @@
     </row>
     <row r="27" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B27" s="4" t="s">
-        <v>1059</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="24" t="s">
-        <v>1060</v>
+        <v>1045</v>
       </c>
       <c r="B28" s="4"/>
     </row>
     <row r="29" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="4" t="s">
-        <v>1061</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4233,13 +4233,13 @@
     </row>
     <row r="34" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B34" s="4" t="s">
-        <v>1062</v>
+        <v>1047</v>
       </c>
       <c r="C34" s="4"/>
     </row>
     <row r="35" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="24" t="s">
-        <v>1063</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4264,7 +4264,7 @@
     </row>
     <row r="40" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C40" s="4" t="s">
-        <v>1064</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4329,7 +4329,7 @@
     </row>
     <row r="53" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B53" s="24" t="s">
-        <v>1065</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4379,7 +4379,7 @@
     </row>
     <row r="63" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B63" s="4" t="s">
-        <v>1066</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="64" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5339,8 +5339,8 @@
     <col min="2" max="2" width="25.7109375" customWidth="1"/>
     <col min="3" max="3" width="7" customWidth="1"/>
     <col min="4" max="4" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="45" customWidth="1"/>
-    <col min="7" max="7" width="28.42578125" customWidth="1"/>
+    <col min="5" max="5" width="196" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="76.42578125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="25.85546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="29.28515625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="27" bestFit="1" customWidth="1"/>
@@ -5392,7 +5392,7 @@
         <v>65</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>1036</v>
+        <v>1021</v>
       </c>
       <c r="E1" s="14" t="s">
         <v>64</v>
@@ -5544,7 +5544,7 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>938</v>
+        <v>923</v>
       </c>
       <c r="E2" t="s">
         <v>108</v>
@@ -5644,7 +5644,7 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>939</v>
+        <v>924</v>
       </c>
       <c r="E3" t="s">
         <v>115</v>
@@ -5744,7 +5744,7 @@
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>940</v>
+        <v>925</v>
       </c>
       <c r="E4" t="s">
         <v>122</v>
@@ -5850,7 +5850,7 @@
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>941</v>
+        <v>926</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>127</v>
@@ -5951,7 +5951,7 @@
         <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>942</v>
+        <v>927</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>134</v>
@@ -6024,7 +6024,7 @@
       <c r="AN6" s="4"/>
       <c r="AO6" s="4"/>
       <c r="AP6" s="4" t="s">
-        <v>136</v>
+        <v>1060</v>
       </c>
       <c r="AQ6" s="4"/>
       <c r="AR6" s="4" t="s">
@@ -6045,31 +6045,31 @@
     </row>
     <row r="7" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>137</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>138</v>
       </c>
       <c r="C7" s="4">
         <v>6</v>
       </c>
       <c r="D7" t="s">
-        <v>943</v>
+        <v>928</v>
       </c>
       <c r="F7" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="G7" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="H7" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="H7" s="4" t="s">
+      <c r="I7" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="I7" s="4" t="s">
+      <c r="J7" s="4" t="s">
         <v>142</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>143</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
@@ -6106,7 +6106,7 @@
         <v>0</v>
       </c>
       <c r="AF7" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AG7" s="4">
         <v>6.0000000000000001E-3</v>
@@ -6125,7 +6125,7 @@
       <c r="AN7" s="4"/>
       <c r="AO7" s="4"/>
       <c r="AP7" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="AQ7" s="4"/>
       <c r="AR7" s="4" t="s">
@@ -6146,31 +6146,31 @@
     </row>
     <row r="8" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>146</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>147</v>
       </c>
       <c r="C8" s="4">
         <v>7</v>
       </c>
       <c r="D8" t="s">
-        <v>944</v>
+        <v>929</v>
       </c>
       <c r="F8" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="G8" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="G8" s="4" t="s">
-        <v>149</v>
-      </c>
       <c r="H8" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="I8" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="J8" s="4" t="s">
         <v>142</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>143</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
@@ -6209,7 +6209,7 @@
         <v>0</v>
       </c>
       <c r="AF8" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AG8" s="4">
         <v>0</v>
@@ -6230,7 +6230,7 @@
       <c r="AN8" s="4"/>
       <c r="AO8" s="4"/>
       <c r="AP8" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="AQ8" s="4"/>
       <c r="AR8" s="4" t="s">
@@ -6251,31 +6251,31 @@
     </row>
     <row r="9" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C9" s="4">
         <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>945</v>
+        <v>930</v>
       </c>
       <c r="E9" t="s">
+        <v>151</v>
+      </c>
+      <c r="F9" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="G9" s="4" t="s">
         <v>153</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>154</v>
       </c>
       <c r="H9" s="4" t="s">
         <v>71</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="J9" s="4"/>
       <c r="K9" s="4" t="b">
@@ -6338,7 +6338,7 @@
       <c r="AN9" s="4"/>
       <c r="AO9" s="4"/>
       <c r="AP9" s="4" t="s">
-        <v>156</v>
+        <v>1061</v>
       </c>
       <c r="AQ9" s="4"/>
       <c r="AR9" s="4"/>
@@ -6353,31 +6353,31 @@
     </row>
     <row r="10" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C10" s="4">
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>946</v>
+        <v>931</v>
       </c>
       <c r="F10" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="I10" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="J10" s="4" t="s">
         <v>160</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="I10" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>162</v>
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
@@ -6388,19 +6388,19 @@
       <c r="O10" s="4"/>
       <c r="P10" s="4"/>
       <c r="Q10" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="R10" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="S10" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="T10" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="U10" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="V10" s="4"/>
       <c r="W10" s="4"/>
@@ -6416,7 +6416,7 @@
         <v>1</v>
       </c>
       <c r="AF10" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AG10" s="4">
         <v>2</v>
@@ -6437,7 +6437,7 @@
       <c r="AN10" s="4"/>
       <c r="AO10" s="4"/>
       <c r="AP10" s="4" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="AQ10" s="4"/>
       <c r="AR10" s="4" t="s">
@@ -6461,22 +6461,22 @@
         <v>129</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C11" s="4">
         <v>10</v>
       </c>
       <c r="D11" t="s">
-        <v>947</v>
+        <v>932</v>
       </c>
       <c r="E11" t="s">
+        <v>163</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="G11" s="4" t="s">
         <v>165</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>167</v>
       </c>
       <c r="H11" s="4" t="s">
         <v>71</v>
@@ -6545,7 +6545,7 @@
       <c r="AN11" s="4"/>
       <c r="AO11" s="4"/>
       <c r="AP11" s="4" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="AQ11" s="4"/>
       <c r="AR11" s="4"/>
@@ -6566,25 +6566,25 @@
     </row>
     <row r="12" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C12" s="4">
         <v>11</v>
       </c>
       <c r="D12" t="s">
-        <v>948</v>
+        <v>933</v>
       </c>
       <c r="E12" t="s">
+        <v>169</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="G12" s="19" t="s">
         <v>171</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="G12" s="19" t="s">
-        <v>173</v>
       </c>
       <c r="H12" s="4" t="s">
         <v>71</v>
@@ -6647,7 +6647,7 @@
       <c r="AN12" s="4"/>
       <c r="AO12" s="4"/>
       <c r="AP12" s="4" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="AQ12" s="4"/>
       <c r="AR12" s="4" t="s">
@@ -6664,25 +6664,25 @@
     </row>
     <row r="13" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C13" s="4">
         <v>12</v>
       </c>
       <c r="D13" t="s">
-        <v>949</v>
+        <v>934</v>
       </c>
       <c r="E13" t="s">
+        <v>175</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="G13" s="4" t="s">
         <v>177</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>179</v>
       </c>
       <c r="H13" s="4" t="s">
         <v>71</v>
@@ -6751,7 +6751,7 @@
       <c r="AN13" s="4"/>
       <c r="AO13" s="4"/>
       <c r="AP13" s="4" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="AQ13" s="4"/>
       <c r="AR13" s="4" t="s">
@@ -6774,25 +6774,25 @@
     </row>
     <row r="14" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C14" s="4">
         <v>13</v>
       </c>
       <c r="D14" t="s">
-        <v>949</v>
+        <v>934</v>
       </c>
       <c r="E14" t="s">
+        <v>181</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="G14" s="4" t="s">
         <v>183</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>185</v>
       </c>
       <c r="H14" s="4" t="s">
         <v>71</v>
@@ -6855,7 +6855,7 @@
       <c r="AN14" s="4"/>
       <c r="AO14" s="4"/>
       <c r="AP14" s="4" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="AQ14" s="4"/>
       <c r="AR14" s="4" t="s">
@@ -6876,25 +6876,25 @@
     </row>
     <row r="15" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C15" s="4">
         <v>14</v>
       </c>
       <c r="D15" t="s">
-        <v>950</v>
+        <v>935</v>
       </c>
       <c r="E15" t="s">
+        <v>187</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="G15" s="4" t="s">
         <v>189</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>191</v>
       </c>
       <c r="H15" s="4" t="s">
         <v>71</v>
@@ -6957,7 +6957,7 @@
       <c r="AN15" s="4"/>
       <c r="AO15" s="4"/>
       <c r="AP15" s="4" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="AQ15" s="4"/>
       <c r="AR15" s="4" t="s">
@@ -6978,25 +6978,25 @@
     </row>
     <row r="16" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C16" s="4">
         <v>15</v>
       </c>
       <c r="D16" t="s">
-        <v>949</v>
+        <v>934</v>
       </c>
       <c r="E16" t="s">
+        <v>193</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="G16" s="4" t="s">
         <v>195</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>197</v>
       </c>
       <c r="H16" s="4" t="s">
         <v>71</v>
@@ -7059,7 +7059,7 @@
       <c r="AN16" s="4"/>
       <c r="AO16" s="4"/>
       <c r="AP16" s="4" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AQ16" s="4"/>
       <c r="AR16" s="4" t="s">
@@ -7080,25 +7080,25 @@
     </row>
     <row r="17" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C17" s="4">
         <v>16</v>
       </c>
       <c r="D17" t="s">
-        <v>951</v>
+        <v>936</v>
       </c>
       <c r="E17" s="24" t="s">
-        <v>1052</v>
+        <v>1037</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H17" s="4" t="s">
         <v>71</v>
@@ -7161,7 +7161,7 @@
       <c r="AN17" s="4"/>
       <c r="AO17" s="4"/>
       <c r="AP17" s="4" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="AQ17" s="4"/>
       <c r="AR17" s="4" t="s">
@@ -7182,31 +7182,31 @@
     </row>
     <row r="18" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C18" s="4">
         <v>17</v>
       </c>
       <c r="D18" t="s">
-        <v>952</v>
+        <v>937</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="J18" s="4" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
@@ -7243,7 +7243,7 @@
         <v>0</v>
       </c>
       <c r="AF18" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AG18" s="4">
         <v>4.0000000000000001E-3</v>
@@ -7262,7 +7262,7 @@
       <c r="AN18" s="4"/>
       <c r="AO18" s="4"/>
       <c r="AP18" s="4" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AQ18" s="4"/>
       <c r="AR18" s="4"/>
@@ -7281,34 +7281,34 @@
     </row>
     <row r="19" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C19" s="4">
         <v>18</v>
       </c>
       <c r="D19" t="s">
-        <v>953</v>
+        <v>938</v>
       </c>
       <c r="E19" s="24" t="s">
-        <v>1053</v>
+        <v>1038</v>
       </c>
       <c r="F19" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="H19" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="G19" s="4" t="s">
+      <c r="I19" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="H19" s="4" t="s">
+      <c r="J19" s="4" t="s">
         <v>213</v>
-      </c>
-      <c r="I19" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="J19" s="4" t="s">
-        <v>215</v>
       </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
@@ -7368,7 +7368,7 @@
       <c r="AN19" s="4"/>
       <c r="AO19" s="4"/>
       <c r="AP19" s="4" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="AQ19" s="4"/>
       <c r="AR19" s="4"/>
@@ -7383,25 +7383,25 @@
     </row>
     <row r="20" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C20" s="4">
         <v>19</v>
       </c>
       <c r="D20" t="s">
-        <v>954</v>
+        <v>939</v>
       </c>
       <c r="E20" s="24" t="s">
-        <v>1054</v>
+        <v>1039</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="H20" s="4" t="s">
         <v>71</v>
@@ -7472,7 +7472,7 @@
       <c r="AN20" s="4"/>
       <c r="AO20" s="4"/>
       <c r="AP20" s="4" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="AQ20" s="4"/>
       <c r="AR20" s="4"/>
@@ -7491,25 +7491,25 @@
     </row>
     <row r="21" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C21" s="4">
         <v>20</v>
       </c>
       <c r="D21" t="s">
-        <v>1015</v>
+        <v>1000</v>
       </c>
       <c r="F21" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="G21" s="19" t="s">
+        <v>223</v>
+      </c>
+      <c r="H21" s="4" t="s">
         <v>224</v>
-      </c>
-      <c r="G21" s="19" t="s">
-        <v>225</v>
-      </c>
-      <c r="H21" s="4" t="s">
-        <v>226</v>
       </c>
       <c r="I21" s="4"/>
       <c r="J21" s="4"/>
@@ -7568,7 +7568,7 @@
       <c r="AN21" s="4"/>
       <c r="AO21" s="4"/>
       <c r="AP21" s="4" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="AQ21" s="4"/>
       <c r="AR21" s="4"/>
@@ -7585,31 +7585,31 @@
     </row>
     <row r="22" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C22" s="4">
         <v>21</v>
       </c>
       <c r="D22" t="s">
-        <v>1016</v>
+        <v>1001</v>
       </c>
       <c r="F22" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="G22" s="19" t="s">
+        <v>229</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="I22" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="G22" s="19" t="s">
+      <c r="J22" s="4" t="s">
         <v>231</v>
-      </c>
-      <c r="H22" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="I22" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="J22" s="4" t="s">
-        <v>233</v>
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
@@ -7645,7 +7645,7 @@
         <v>1</v>
       </c>
       <c r="AF22" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AG22" s="4"/>
       <c r="AH22" s="4"/>
@@ -7660,7 +7660,7 @@
       <c r="AN22" s="4"/>
       <c r="AO22" s="4"/>
       <c r="AP22" s="4" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="AQ22" s="4"/>
       <c r="AR22" s="4"/>
@@ -7677,25 +7677,25 @@
     </row>
     <row r="23" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C23" s="4">
         <v>22</v>
       </c>
       <c r="D23" t="s">
-        <v>955</v>
+        <v>940</v>
       </c>
       <c r="E23" t="s">
+        <v>235</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="G23" s="4" t="s">
         <v>237</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="G23" s="4" t="s">
-        <v>239</v>
       </c>
       <c r="H23" s="4" t="s">
         <v>71</v>
@@ -7758,7 +7758,7 @@
       <c r="AN23" s="4"/>
       <c r="AO23" s="4"/>
       <c r="AP23" s="4" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="AQ23" s="4"/>
       <c r="AR23" s="4"/>
@@ -7773,34 +7773,34 @@
     </row>
     <row r="24" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C24" s="4">
         <v>23</v>
       </c>
       <c r="D24" t="s">
-        <v>956</v>
+        <v>941</v>
       </c>
       <c r="E24" t="s">
+        <v>241</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="G24" s="4" t="s">
         <v>243</v>
       </c>
-      <c r="F24" s="4" t="s">
+      <c r="H24" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="I24" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="J24" s="4" t="s">
         <v>244</v>
-      </c>
-      <c r="G24" s="4" t="s">
-        <v>245</v>
-      </c>
-      <c r="H24" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="I24" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="J24" s="4" t="s">
-        <v>246</v>
       </c>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
@@ -7852,7 +7852,7 @@
       <c r="AN24" s="4"/>
       <c r="AO24" s="4"/>
       <c r="AP24" s="4" t="s">
-        <v>247</v>
+        <v>1062</v>
       </c>
       <c r="AQ24" s="4"/>
       <c r="AR24" s="4"/>
@@ -7867,31 +7867,31 @@
     </row>
     <row r="25" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="C25" s="4">
         <v>24</v>
       </c>
       <c r="D25" t="s">
-        <v>957</v>
+        <v>942</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
@@ -7937,7 +7937,7 @@
       </c>
       <c r="AH25" s="4"/>
       <c r="AI25" s="4" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="AJ25" s="4"/>
       <c r="AK25" s="4"/>
@@ -7949,7 +7949,7 @@
       <c r="AN25" s="4"/>
       <c r="AO25" s="4"/>
       <c r="AP25" s="4" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="AQ25" s="4"/>
       <c r="AR25" s="4"/>
@@ -7966,34 +7966,34 @@
     </row>
     <row r="26" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="C26" s="4">
         <v>25</v>
       </c>
       <c r="D26" t="s">
-        <v>958</v>
+        <v>943</v>
       </c>
       <c r="E26" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
@@ -8039,7 +8039,7 @@
       </c>
       <c r="AH26" s="4"/>
       <c r="AI26" s="4" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="AJ26" s="4"/>
       <c r="AK26" s="4"/>
@@ -8051,7 +8051,7 @@
       <c r="AN26" s="4"/>
       <c r="AO26" s="4"/>
       <c r="AP26" s="4" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="AQ26" s="4"/>
       <c r="AR26" s="4"/>
@@ -8068,34 +8068,34 @@
     </row>
     <row r="27" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="4" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C27" s="4">
         <v>26</v>
       </c>
       <c r="D27" t="s">
-        <v>959</v>
+        <v>944</v>
       </c>
       <c r="E27" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I27" s="4" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
@@ -8151,7 +8151,7 @@
       </c>
       <c r="AO27" s="4"/>
       <c r="AP27" s="4" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="AQ27" s="4"/>
       <c r="AR27" s="4"/>
@@ -8166,34 +8166,34 @@
     </row>
     <row r="28" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="4" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="C28" s="4">
         <v>27</v>
       </c>
       <c r="D28" t="s">
-        <v>960</v>
+        <v>945</v>
       </c>
       <c r="E28" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="J28" s="4" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
@@ -8247,7 +8247,7 @@
       <c r="AN28" s="4"/>
       <c r="AO28" s="4"/>
       <c r="AP28" s="4" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="AQ28" s="4"/>
       <c r="AR28" s="4"/>
@@ -8262,25 +8262,25 @@
     </row>
     <row r="29" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="4" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="C29" s="4">
         <v>28</v>
       </c>
       <c r="D29" t="s">
-        <v>961</v>
+        <v>946</v>
       </c>
       <c r="E29" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="H29" s="4" t="s">
         <v>71</v>
@@ -8289,7 +8289,7 @@
         <v>129</v>
       </c>
       <c r="J29" s="4" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="K29" s="4" t="b">
         <v>1</v>
@@ -8343,7 +8343,7 @@
       <c r="AN29" s="4"/>
       <c r="AO29" s="4"/>
       <c r="AP29" s="4" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="AQ29" s="4"/>
       <c r="AR29" s="4"/>
@@ -8362,25 +8362,25 @@
     </row>
     <row r="30" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="4" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="C30" s="4">
         <v>29</v>
       </c>
       <c r="D30" t="s">
-        <v>961</v>
+        <v>946</v>
       </c>
       <c r="E30" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="H30" s="4" t="s">
         <v>71</v>
@@ -8389,7 +8389,7 @@
         <v>129</v>
       </c>
       <c r="J30" s="4" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="K30" s="4" t="b">
         <v>1</v>
@@ -8443,7 +8443,7 @@
       <c r="AN30" s="4"/>
       <c r="AO30" s="4"/>
       <c r="AP30" s="4" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="AQ30" s="4"/>
       <c r="AR30" s="4"/>
@@ -8462,25 +8462,25 @@
     </row>
     <row r="31" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="4" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="C31" s="4">
         <v>30</v>
       </c>
       <c r="D31" t="s">
-        <v>961</v>
+        <v>946</v>
       </c>
       <c r="E31" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="H31" s="4" t="s">
         <v>71</v>
@@ -8489,7 +8489,7 @@
         <v>129</v>
       </c>
       <c r="J31" s="4" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="K31" s="4" t="b">
         <v>1</v>
@@ -8543,7 +8543,7 @@
       <c r="AN31" s="4"/>
       <c r="AO31" s="4"/>
       <c r="AP31" s="4" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="AQ31" s="4"/>
       <c r="AR31" s="4"/>
@@ -8562,31 +8562,31 @@
     </row>
     <row r="32" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="4" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="C32" s="4">
         <v>31</v>
       </c>
       <c r="D32" t="s">
-        <v>962</v>
+        <v>947</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I32" s="4" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="J32" s="4" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
@@ -8623,7 +8623,7 @@
         <v>0</v>
       </c>
       <c r="AF32" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AG32" s="4">
         <v>5.0000000000000001E-3</v>
@@ -8644,7 +8644,7 @@
       <c r="AN32" s="4"/>
       <c r="AO32" s="4"/>
       <c r="AP32" s="4" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="AQ32" s="4"/>
       <c r="AR32" s="4" t="s">
@@ -8665,31 +8665,31 @@
     </row>
     <row r="33" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="4" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="C33" s="4">
         <v>32</v>
       </c>
       <c r="D33" t="s">
-        <v>1017</v>
+        <v>1002</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="G33" s="20" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I33" s="4" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="J33" s="4" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
@@ -8725,7 +8725,7 @@
         <v>0</v>
       </c>
       <c r="AF33" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AG33" s="4"/>
       <c r="AH33" s="4"/>
@@ -8740,7 +8740,7 @@
       <c r="AN33" s="4"/>
       <c r="AO33" s="4"/>
       <c r="AP33" s="4" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="AQ33" s="4"/>
       <c r="AR33" s="4" t="s">
@@ -8759,34 +8759,34 @@
     </row>
     <row r="34" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="4" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="C34" s="4">
         <v>33</v>
       </c>
       <c r="D34" t="s">
-        <v>963</v>
+        <v>948</v>
       </c>
       <c r="E34" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I34" s="4" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="J34" s="4" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
@@ -8844,7 +8844,7 @@
       </c>
       <c r="AO34" s="4"/>
       <c r="AP34" s="4" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="AQ34" s="4"/>
       <c r="AR34" s="4"/>
@@ -8863,25 +8863,25 @@
     </row>
     <row r="35" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="4" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="C35" s="4">
         <v>34</v>
       </c>
       <c r="D35" t="s">
-        <v>1018</v>
+        <v>1003</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G35" s="20" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="I35" s="4"/>
       <c r="J35" s="4"/>
@@ -8936,7 +8936,7 @@
       <c r="AN35" s="4"/>
       <c r="AO35" s="4"/>
       <c r="AP35" s="4" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="AQ35" s="4"/>
       <c r="AR35" s="4"/>
@@ -8953,34 +8953,34 @@
     </row>
     <row r="36" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="4" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="C36" s="4">
         <v>35</v>
       </c>
       <c r="D36" t="s">
-        <v>964</v>
+        <v>949</v>
       </c>
       <c r="E36" t="s">
+        <v>312</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="G36" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="H36" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="I36" s="4" t="s">
         <v>315</v>
       </c>
-      <c r="F36" s="4" t="s">
+      <c r="J36" s="4" t="s">
         <v>316</v>
-      </c>
-      <c r="G36" s="4" t="s">
-        <v>317</v>
-      </c>
-      <c r="H36" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="I36" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="J36" s="4" t="s">
-        <v>319</v>
       </c>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
@@ -9028,7 +9028,7 @@
         <v>2E-3</v>
       </c>
       <c r="AI36" s="4" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="AJ36" s="4"/>
       <c r="AK36" s="4"/>
@@ -9044,10 +9044,10 @@
         <v>59</v>
       </c>
       <c r="AP36" s="4" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="AQ36" s="4" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="AR36" s="4"/>
       <c r="AS36" s="4" t="b">
@@ -9061,34 +9061,34 @@
     </row>
     <row r="37" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="4" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>1050</v>
+        <v>1035</v>
       </c>
       <c r="C37" s="4">
         <v>36</v>
       </c>
       <c r="D37" t="s">
-        <v>964</v>
+        <v>949</v>
       </c>
       <c r="E37" s="24" t="s">
-        <v>1049</v>
+        <v>1034</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I37" s="4" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="J37" s="4" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
@@ -9136,7 +9136,7 @@
         <v>2E-3</v>
       </c>
       <c r="AI37" s="4" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="AJ37" s="4"/>
       <c r="AK37" s="4"/>
@@ -9152,10 +9152,10 @@
         <v>59</v>
       </c>
       <c r="AP37" s="4" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="AQ37" s="4" t="s">
-        <v>1051</v>
+        <v>1036</v>
       </c>
       <c r="AR37" s="4"/>
       <c r="AS37" s="4" t="b">
@@ -9169,31 +9169,31 @@
     </row>
     <row r="38" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="4" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="C38" s="4">
         <v>37</v>
       </c>
       <c r="D38" t="s">
-        <v>1019</v>
+        <v>1004</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="G38" s="20" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I38" s="4" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="J38" s="4" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
@@ -9229,7 +9229,7 @@
         <v>1</v>
       </c>
       <c r="AF38" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AG38" s="4"/>
       <c r="AH38" s="4"/>
@@ -9246,7 +9246,7 @@
       <c r="AN38" s="4"/>
       <c r="AO38" s="4"/>
       <c r="AP38" s="4" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="AQ38" s="4"/>
       <c r="AR38" s="4"/>
@@ -9263,21 +9263,21 @@
     </row>
     <row r="39" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="4" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="C39" s="4">
         <v>38</v>
       </c>
       <c r="D39" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="F39" s="4"/>
       <c r="G39" s="4"/>
       <c r="H39" s="4" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="I39" s="4"/>
       <c r="J39" s="4"/>
@@ -9324,7 +9324,7 @@
         <v>0.8</v>
       </c>
       <c r="AI39" s="4" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="AJ39" s="4"/>
       <c r="AK39" s="4"/>
@@ -9336,7 +9336,7 @@
       <c r="AN39" s="4"/>
       <c r="AO39" s="4"/>
       <c r="AP39" s="4" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="AQ39" s="4"/>
       <c r="AR39" s="4"/>
@@ -9353,25 +9353,25 @@
     </row>
     <row r="40" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="4" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="C40" s="4">
         <v>39</v>
       </c>
       <c r="D40" t="s">
-        <v>1020</v>
+        <v>1005</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="G40" s="20" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="I40" s="4"/>
       <c r="J40" s="4"/>
@@ -9430,7 +9430,7 @@
       <c r="AN40" s="4"/>
       <c r="AO40" s="4"/>
       <c r="AP40" s="4" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="AQ40" s="4"/>
       <c r="AR40" s="4"/>
@@ -9447,25 +9447,25 @@
     </row>
     <row r="41" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="4" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="C41" s="4">
         <v>40</v>
       </c>
       <c r="D41" t="s">
-        <v>965</v>
+        <v>950</v>
       </c>
       <c r="E41" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="H41" s="4" t="s">
         <v>71</v>
@@ -9532,7 +9532,7 @@
       <c r="AN41" s="4"/>
       <c r="AO41" s="4"/>
       <c r="AP41" s="4" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="AQ41" s="4"/>
       <c r="AR41" s="4"/>
@@ -9551,34 +9551,34 @@
     </row>
     <row r="42" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="4" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="C42" s="4">
         <v>41</v>
       </c>
       <c r="D42" t="s">
-        <v>966</v>
+        <v>951</v>
       </c>
       <c r="E42" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I42" s="4" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="J42" s="4" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
@@ -9630,7 +9630,7 @@
       <c r="AN42" s="4"/>
       <c r="AO42" s="4"/>
       <c r="AP42" s="4" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="AQ42" s="4"/>
       <c r="AR42" s="4"/>
@@ -9645,34 +9645,34 @@
     </row>
     <row r="43" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="4" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="C43" s="4">
         <v>42</v>
       </c>
       <c r="D43" t="s">
-        <v>967</v>
+        <v>952</v>
       </c>
       <c r="E43" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I43" s="4" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="J43" s="4" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
@@ -9728,7 +9728,7 @@
       <c r="AN43" s="4"/>
       <c r="AO43" s="4"/>
       <c r="AP43" s="4" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="AQ43" s="4"/>
       <c r="AR43" s="4"/>
@@ -9747,34 +9747,34 @@
     </row>
     <row r="44" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="4" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="C44" s="4">
         <v>43</v>
       </c>
       <c r="D44" t="s">
-        <v>968</v>
+        <v>953</v>
       </c>
       <c r="E44" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I44" s="4" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="J44" s="4" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
@@ -9820,7 +9820,7 @@
       </c>
       <c r="AH44" s="4"/>
       <c r="AI44" s="4" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="AJ44" s="4"/>
       <c r="AK44" s="4"/>
@@ -9832,7 +9832,7 @@
       <c r="AN44" s="4"/>
       <c r="AO44" s="4"/>
       <c r="AP44" s="4" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="AQ44" s="4"/>
       <c r="AR44" s="4"/>
@@ -9849,34 +9849,34 @@
     </row>
     <row r="45" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="4" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="C45" s="4">
         <v>44</v>
       </c>
       <c r="D45" t="s">
-        <v>969</v>
+        <v>954</v>
       </c>
       <c r="E45" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I45" s="4" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="J45" s="4" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
@@ -9928,7 +9928,7 @@
       <c r="AN45" s="4"/>
       <c r="AO45" s="4"/>
       <c r="AP45" s="4" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="AQ45" s="4"/>
       <c r="AR45" s="4"/>
@@ -9943,25 +9943,25 @@
     </row>
     <row r="46" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="4" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="C46" s="4">
         <v>45</v>
       </c>
       <c r="D46" t="s">
-        <v>970</v>
+        <v>955</v>
       </c>
       <c r="E46" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="H46" s="4" t="s">
         <v>71</v>
@@ -9970,7 +9970,7 @@
         <v>129</v>
       </c>
       <c r="J46" s="4" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="K46" s="4" t="b">
         <v>1</v>
@@ -10024,7 +10024,7 @@
       <c r="AN46" s="4"/>
       <c r="AO46" s="4"/>
       <c r="AP46" s="4" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="AQ46" s="4"/>
       <c r="AR46" s="4"/>
@@ -10039,25 +10039,25 @@
     </row>
     <row r="47" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="4" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="C47" s="4">
         <v>46</v>
       </c>
       <c r="D47" t="s">
-        <v>970</v>
+        <v>955</v>
       </c>
       <c r="E47" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="H47" s="4" t="s">
         <v>71</v>
@@ -10066,7 +10066,7 @@
         <v>129</v>
       </c>
       <c r="J47" s="4" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="K47" s="4" t="b">
         <v>1</v>
@@ -10120,7 +10120,7 @@
       <c r="AN47" s="4"/>
       <c r="AO47" s="4"/>
       <c r="AP47" s="4" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="AQ47" s="4"/>
       <c r="AR47" s="4"/>
@@ -10135,31 +10135,31 @@
     </row>
     <row r="48" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="4" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="C48" s="4">
         <v>47</v>
       </c>
       <c r="D48" t="s">
-        <v>1021</v>
+        <v>1006</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="G48" s="20" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I48" s="4" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="J48" s="4" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
@@ -10197,7 +10197,7 @@
         <v>0</v>
       </c>
       <c r="AF48" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AG48" s="4">
         <v>0.1</v>
@@ -10216,7 +10216,7 @@
       <c r="AN48" s="4"/>
       <c r="AO48" s="4"/>
       <c r="AP48" s="4" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="AQ48" s="4"/>
       <c r="AR48" s="4" t="s">
@@ -10235,25 +10235,25 @@
     </row>
     <row r="49" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="4" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="C49" s="4">
         <v>48</v>
       </c>
       <c r="D49" t="s">
-        <v>948</v>
+        <v>933</v>
       </c>
       <c r="E49" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="H49" s="4" t="s">
         <v>71</v>
@@ -10316,7 +10316,7 @@
       <c r="AN49" s="4"/>
       <c r="AO49" s="4"/>
       <c r="AP49" s="4" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="AQ49" s="4"/>
       <c r="AR49" s="4" t="s">
@@ -10337,21 +10337,21 @@
     </row>
     <row r="50" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="4" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="C50" s="4">
         <v>49</v>
       </c>
       <c r="D50" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="F50" s="4"/>
       <c r="G50" s="4"/>
       <c r="H50" s="4" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="I50" s="4"/>
       <c r="J50" s="4"/>
@@ -10362,19 +10362,19 @@
       <c r="O50" s="4"/>
       <c r="P50" s="4"/>
       <c r="Q50" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="R50" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="S50" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="T50" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="U50" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="V50" s="4"/>
       <c r="W50" s="4"/>
@@ -10386,10 +10386,10 @@
       <c r="AC50" s="4"/>
       <c r="AD50" s="4"/>
       <c r="AE50" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AF50" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AG50" s="4"/>
       <c r="AH50" s="4"/>
@@ -10404,7 +10404,7 @@
       <c r="AN50" s="4"/>
       <c r="AO50" s="4"/>
       <c r="AP50" s="4" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="AQ50" s="4"/>
       <c r="AR50" s="4"/>
@@ -10419,31 +10419,31 @@
     </row>
     <row r="51" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="4" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="C51" s="4">
         <v>50</v>
       </c>
       <c r="D51" t="s">
-        <v>971</v>
+        <v>956</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="H51" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I51" s="4" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="J51" s="4" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
@@ -10482,21 +10482,21 @@
         <v>1</v>
       </c>
       <c r="AF51" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AG51" s="4">
         <v>1.3</v>
       </c>
       <c r="AH51" s="4"/>
       <c r="AI51" s="4" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="AJ51" s="4">
         <v>1</v>
       </c>
       <c r="AK51" s="4"/>
       <c r="AL51" s="4" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="AM51" s="4" t="b">
         <f t="shared" si="1"/>
@@ -10505,7 +10505,7 @@
       <c r="AN51" s="4"/>
       <c r="AO51" s="4"/>
       <c r="AP51" s="4" t="s">
-        <v>404</v>
+        <v>1063</v>
       </c>
       <c r="AQ51" s="4"/>
       <c r="AR51" s="4" t="s">
@@ -10528,34 +10528,34 @@
     </row>
     <row r="52" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="4" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C52" s="4">
         <v>51</v>
       </c>
       <c r="D52" t="s">
-        <v>972</v>
+        <v>957</v>
       </c>
       <c r="E52" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I52" s="4" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="J52" s="4" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
@@ -10613,7 +10613,7 @@
       <c r="AN52" s="4"/>
       <c r="AO52" s="4"/>
       <c r="AP52" s="4" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="AQ52" s="4"/>
       <c r="AR52" s="4"/>
@@ -10628,27 +10628,27 @@
     </row>
     <row r="53" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="4" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="C53" s="4">
         <v>52</v>
       </c>
       <c r="D53" t="s">
-        <v>1022</v>
+        <v>1007</v>
       </c>
       <c r="F53" s="4"/>
       <c r="G53" s="4"/>
       <c r="H53" s="4" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I53" s="4" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="J53" s="4" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
@@ -10701,7 +10701,7 @@
       <c r="AN53" s="4"/>
       <c r="AO53" s="4"/>
       <c r="AP53" s="4" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="AQ53" s="4"/>
       <c r="AR53" s="4"/>
@@ -10716,34 +10716,34 @@
     </row>
     <row r="54" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="4" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="C54" s="4">
         <v>53</v>
       </c>
       <c r="D54" t="s">
-        <v>973</v>
+        <v>958</v>
       </c>
       <c r="E54" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="H54" s="4" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I54" s="4" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="J54" s="4" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>
@@ -10789,7 +10789,7 @@
       </c>
       <c r="AH54" s="4"/>
       <c r="AI54" s="4" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="AJ54" s="4"/>
       <c r="AK54" s="4"/>
@@ -10801,7 +10801,7 @@
       <c r="AN54" s="4"/>
       <c r="AO54" s="4"/>
       <c r="AP54" s="4" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="AQ54" s="4"/>
       <c r="AR54" s="4"/>
@@ -10818,34 +10818,34 @@
     </row>
     <row r="55" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="4" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="C55" s="4">
         <v>54</v>
       </c>
       <c r="D55" t="s">
-        <v>974</v>
+        <v>959</v>
       </c>
       <c r="E55" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="G55" s="19" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="H55" s="4" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I55" s="4" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="J55" s="4" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="K55" s="4"/>
       <c r="L55" s="4"/>
@@ -10905,7 +10905,7 @@
       <c r="AN55" s="4"/>
       <c r="AO55" s="4"/>
       <c r="AP55" s="4" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="AQ55" s="4"/>
       <c r="AR55" s="4"/>
@@ -10924,34 +10924,34 @@
     </row>
     <row r="56" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="4" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="C56" s="4">
         <v>55</v>
       </c>
       <c r="D56" t="s">
-        <v>975</v>
+        <v>960</v>
       </c>
       <c r="E56" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="H56" s="4" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I56" s="4" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="J56" s="4" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="K56" s="4"/>
       <c r="L56" s="4"/>
@@ -11003,7 +11003,7 @@
       <c r="AN56" s="4"/>
       <c r="AO56" s="4"/>
       <c r="AP56" s="4" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="AQ56" s="4"/>
       <c r="AR56" s="4"/>
@@ -11018,27 +11018,27 @@
     </row>
     <row r="57" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="4" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="C57" s="4">
         <v>56</v>
       </c>
       <c r="D57" t="s">
-        <v>1023</v>
+        <v>1008</v>
       </c>
       <c r="F57" s="4"/>
       <c r="G57" s="4"/>
       <c r="H57" s="4" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I57" s="4" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="J57" s="4" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="K57" s="4"/>
       <c r="L57" s="4"/>
@@ -11091,7 +11091,7 @@
       <c r="AN57" s="4"/>
       <c r="AO57" s="4"/>
       <c r="AP57" s="4" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="AQ57" s="4"/>
       <c r="AR57" s="4"/>
@@ -11106,25 +11106,25 @@
     </row>
     <row r="58" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="4" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="C58" s="4">
         <v>57</v>
       </c>
       <c r="D58" t="s">
-        <v>976</v>
+        <v>961</v>
       </c>
       <c r="E58" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="H58" s="4" t="s">
         <v>71</v>
@@ -11191,7 +11191,7 @@
       <c r="AN58" s="4"/>
       <c r="AO58" s="4"/>
       <c r="AP58" s="4" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="AQ58" s="4"/>
       <c r="AR58" s="4"/>
@@ -11210,25 +11210,25 @@
     </row>
     <row r="59" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="4" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="C59" s="4">
         <v>58</v>
       </c>
       <c r="D59" t="s">
-        <v>976</v>
+        <v>961</v>
       </c>
       <c r="E59" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="H59" s="4" t="s">
         <v>71</v>
@@ -11291,7 +11291,7 @@
       <c r="AN59" s="4"/>
       <c r="AO59" s="4"/>
       <c r="AP59" s="4" t="s">
-        <v>445</v>
+        <v>1064</v>
       </c>
       <c r="AQ59" s="4"/>
       <c r="AR59" s="4"/>
@@ -11306,25 +11306,25 @@
     </row>
     <row r="60" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="4" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="C60" s="4">
         <v>59</v>
       </c>
       <c r="D60" t="s">
-        <v>976</v>
+        <v>961</v>
       </c>
       <c r="E60" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="H60" s="4" t="s">
         <v>71</v>
@@ -11391,7 +11391,7 @@
       <c r="AN60" s="4"/>
       <c r="AO60" s="4"/>
       <c r="AP60" s="4" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="AQ60" s="4"/>
       <c r="AR60" s="4"/>
@@ -11410,34 +11410,34 @@
     </row>
     <row r="61" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="4" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="C61" s="4">
         <v>60</v>
       </c>
       <c r="D61" t="s">
-        <v>977</v>
+        <v>962</v>
       </c>
       <c r="E61" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="G61" s="19" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="H61" s="4" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I61" s="4" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="J61" s="4" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="K61" s="4"/>
       <c r="L61" s="4"/>
@@ -11491,7 +11491,7 @@
       </c>
       <c r="AO61" s="4"/>
       <c r="AP61" s="4" t="s">
-        <v>457</v>
+        <v>1065</v>
       </c>
       <c r="AQ61" s="4"/>
       <c r="AR61" s="4"/>
@@ -11506,34 +11506,34 @@
     </row>
     <row r="62" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="4" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="C62" s="4">
         <v>61</v>
       </c>
       <c r="D62" t="s">
-        <v>978</v>
+        <v>963</v>
       </c>
       <c r="E62" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="H62" s="4" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I62" s="4" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="J62" s="4" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="K62" s="4"/>
       <c r="L62" s="4"/>
@@ -11585,7 +11585,7 @@
       <c r="AN62" s="4"/>
       <c r="AO62" s="4"/>
       <c r="AP62" s="4" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="AQ62" s="4"/>
       <c r="AR62" s="4"/>
@@ -11600,34 +11600,34 @@
     </row>
     <row r="63" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="4" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="C63" s="4">
         <v>62</v>
       </c>
       <c r="D63" t="s">
-        <v>978</v>
+        <v>963</v>
       </c>
       <c r="E63" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="H63" s="4" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I63" s="4" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="J63" s="4" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="K63" s="4"/>
       <c r="L63" s="4"/>
@@ -11683,7 +11683,7 @@
       <c r="AN63" s="4"/>
       <c r="AO63" s="4"/>
       <c r="AP63" s="4" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="AQ63" s="4"/>
       <c r="AR63" s="4"/>
@@ -11702,34 +11702,34 @@
     </row>
     <row r="64" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="4" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="C64" s="4">
         <v>63</v>
       </c>
       <c r="D64" t="s">
-        <v>979</v>
+        <v>964</v>
       </c>
       <c r="E64" t="s">
-        <v>1040</v>
+        <v>1025</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="G64" s="4" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="H64" s="4" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I64" s="4" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="J64" s="4" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="K64" s="4"/>
       <c r="L64" s="4"/>
@@ -11785,7 +11785,7 @@
       <c r="AN64" s="4"/>
       <c r="AO64" s="4"/>
       <c r="AP64" s="4" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="AQ64" s="4"/>
       <c r="AR64" s="4"/>
@@ -11804,34 +11804,34 @@
     </row>
     <row r="65" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="4" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="C65" s="4">
         <v>64</v>
       </c>
       <c r="D65" t="s">
-        <v>979</v>
+        <v>964</v>
       </c>
       <c r="E65" t="s">
-        <v>1041</v>
+        <v>1026</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="H65" s="4" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I65" s="4" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="J65" s="4" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="K65" s="4"/>
       <c r="L65" s="4"/>
@@ -11887,7 +11887,7 @@
       <c r="AN65" s="4"/>
       <c r="AO65" s="4"/>
       <c r="AP65" s="4" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="AQ65" s="4"/>
       <c r="AR65" s="4"/>
@@ -11906,27 +11906,27 @@
     </row>
     <row r="66" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="4" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="C66" s="4">
         <v>65</v>
       </c>
       <c r="D66" t="s">
-        <v>979</v>
+        <v>964</v>
       </c>
       <c r="F66" s="4"/>
       <c r="G66" s="4"/>
       <c r="H66" s="4" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I66" s="4" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="J66" s="4" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="K66" s="4"/>
       <c r="L66" s="4"/>
@@ -11977,7 +11977,7 @@
       <c r="AN66" s="4"/>
       <c r="AO66" s="4"/>
       <c r="AP66" s="4" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="AQ66" s="4"/>
       <c r="AR66" s="4"/>
@@ -11992,34 +11992,34 @@
     </row>
     <row r="67" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="4" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="C67" s="4">
         <v>66</v>
       </c>
       <c r="D67" t="s">
-        <v>979</v>
+        <v>964</v>
       </c>
       <c r="E67" t="s">
-        <v>1042</v>
+        <v>1027</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="H67" s="4" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I67" s="4" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="J67" s="4" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="K67" s="4"/>
       <c r="L67" s="4"/>
@@ -12075,7 +12075,7 @@
       <c r="AN67" s="4"/>
       <c r="AO67" s="4"/>
       <c r="AP67" s="4" t="s">
-        <v>487</v>
+        <v>481</v>
       </c>
       <c r="AQ67" s="4"/>
       <c r="AR67" s="4"/>
@@ -12094,31 +12094,31 @@
     </row>
     <row r="68" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="4" t="s">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>489</v>
+        <v>483</v>
       </c>
       <c r="C68" s="4">
         <v>67</v>
       </c>
       <c r="D68" t="s">
-        <v>980</v>
+        <v>965</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="G68" s="4" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="H68" s="4" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I68" s="4" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="J68" s="4" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="K68" s="4"/>
       <c r="L68" s="4"/>
@@ -12174,7 +12174,7 @@
       <c r="AN68" s="4"/>
       <c r="AO68" s="4"/>
       <c r="AP68" s="4" t="s">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="AQ68" s="4"/>
       <c r="AR68" s="4"/>
@@ -12193,31 +12193,31 @@
     </row>
     <row r="69" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="4" t="s">
-        <v>493</v>
+        <v>487</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="C69" s="4">
         <v>68</v>
       </c>
       <c r="D69" t="s">
-        <v>980</v>
+        <v>965</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="H69" s="4" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I69" s="4" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="J69" s="4" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="K69" s="4"/>
       <c r="L69" s="4"/>
@@ -12269,11 +12269,11 @@
       <c r="AN69" s="4"/>
       <c r="AO69" s="4"/>
       <c r="AP69" s="4" t="s">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="AQ69" s="4"/>
       <c r="AR69" s="4" t="s">
-        <v>1038</v>
+        <v>1023</v>
       </c>
       <c r="AS69" s="4" t="b">
         <v>1</v>
@@ -12286,34 +12286,34 @@
     </row>
     <row r="70" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="4" t="s">
-        <v>499</v>
+        <v>493</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="C70" s="4">
         <v>69</v>
       </c>
       <c r="D70" t="s">
-        <v>980</v>
+        <v>965</v>
       </c>
       <c r="E70" t="s">
-        <v>501</v>
+        <v>495</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>502</v>
+        <v>496</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>503</v>
+        <v>497</v>
       </c>
       <c r="H70" s="4" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I70" s="4" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="J70" s="4" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="K70" s="4"/>
       <c r="L70" s="4"/>
@@ -12365,7 +12365,7 @@
       <c r="AN70" s="4"/>
       <c r="AO70" s="4"/>
       <c r="AP70" s="4" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="AQ70" s="4"/>
       <c r="AR70" s="4"/>
@@ -12380,31 +12380,31 @@
     </row>
     <row r="71" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="4" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="C71" s="4">
         <v>70</v>
       </c>
       <c r="D71" t="s">
-        <v>981</v>
+        <v>966</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>508</v>
+        <v>502</v>
       </c>
       <c r="H71" s="4" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I71" s="4" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="J71" s="4" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="K71" s="4"/>
       <c r="L71" s="4"/>
@@ -12456,7 +12456,7 @@
       <c r="AN71" s="4"/>
       <c r="AO71" s="4"/>
       <c r="AP71" s="4" t="s">
-        <v>509</v>
+        <v>503</v>
       </c>
       <c r="AQ71" s="4"/>
       <c r="AR71" s="4"/>
@@ -12471,34 +12471,34 @@
     </row>
     <row r="72" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="4" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="C72" s="4">
         <v>71</v>
       </c>
       <c r="D72" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="E72" t="s">
-        <v>512</v>
+        <v>506</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>513</v>
+        <v>507</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="H72" s="4" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I72" s="4" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="J72" s="4" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="K72" s="4"/>
       <c r="L72" s="4"/>
@@ -12552,7 +12552,7 @@
       <c r="AN72" s="4"/>
       <c r="AO72" s="4"/>
       <c r="AP72" s="4" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="AQ72" s="4"/>
       <c r="AR72" s="4"/>
@@ -12567,34 +12567,34 @@
     </row>
     <row r="73" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="4" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>517</v>
+        <v>511</v>
       </c>
       <c r="C73" s="4">
         <v>72</v>
       </c>
       <c r="D73" t="s">
-        <v>981</v>
+        <v>966</v>
       </c>
       <c r="E73" t="s">
-        <v>518</v>
+        <v>512</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>519</v>
+        <v>513</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>520</v>
+        <v>514</v>
       </c>
       <c r="H73" s="4" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I73" s="4" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="J73" s="4" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="K73" s="4"/>
       <c r="L73" s="4"/>
@@ -12648,7 +12648,7 @@
       <c r="AN73" s="4"/>
       <c r="AO73" s="4"/>
       <c r="AP73" s="4" t="s">
-        <v>521</v>
+        <v>515</v>
       </c>
       <c r="AQ73" s="4"/>
       <c r="AR73" s="4"/>
@@ -12663,34 +12663,34 @@
     </row>
     <row r="74" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="4" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>523</v>
+        <v>517</v>
       </c>
       <c r="C74" s="4">
         <v>73</v>
       </c>
       <c r="D74" t="s">
-        <v>981</v>
+        <v>966</v>
       </c>
       <c r="E74" t="s">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="H74" s="4" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I74" s="4" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="J74" s="4" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="K74" s="4"/>
       <c r="L74" s="4"/>
@@ -12744,7 +12744,7 @@
       <c r="AN74" s="4"/>
       <c r="AO74" s="4"/>
       <c r="AP74" s="4" t="s">
-        <v>527</v>
+        <v>521</v>
       </c>
       <c r="AQ74" s="4"/>
       <c r="AR74" s="4"/>
@@ -12759,34 +12759,34 @@
     </row>
     <row r="75" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="4" t="s">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="C75" s="4">
         <v>74</v>
       </c>
       <c r="D75" t="s">
-        <v>982</v>
+        <v>967</v>
       </c>
       <c r="E75" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="H75" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="I75" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="J75" s="4" t="s">
         <v>213</v>
-      </c>
-      <c r="I75" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="J75" s="4" t="s">
-        <v>215</v>
       </c>
       <c r="K75" s="4"/>
       <c r="L75" s="4"/>
@@ -12840,7 +12840,7 @@
       <c r="AN75" s="4"/>
       <c r="AO75" s="4"/>
       <c r="AP75" s="4" t="s">
-        <v>532</v>
+        <v>526</v>
       </c>
       <c r="AQ75" s="4"/>
       <c r="AR75" s="4"/>
@@ -12855,34 +12855,34 @@
     </row>
     <row r="76" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="4" t="s">
-        <v>533</v>
+        <v>527</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>533</v>
+        <v>527</v>
       </c>
       <c r="C76" s="4">
         <v>75</v>
       </c>
       <c r="D76" t="s">
-        <v>983</v>
+        <v>968</v>
       </c>
       <c r="E76" t="s">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>535</v>
+        <v>529</v>
       </c>
       <c r="G76" s="4" t="s">
-        <v>536</v>
+        <v>530</v>
       </c>
       <c r="H76" s="4" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I76" s="4" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="J76" s="4" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="K76" s="4"/>
       <c r="L76" s="4"/>
@@ -12946,7 +12946,7 @@
         <v>59</v>
       </c>
       <c r="AP76" s="4" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
       <c r="AQ76" s="4"/>
       <c r="AR76" s="4"/>
@@ -12961,34 +12961,34 @@
     </row>
     <row r="77" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="4" t="s">
-        <v>538</v>
+        <v>532</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>539</v>
+        <v>533</v>
       </c>
       <c r="C77" s="4">
         <v>76</v>
       </c>
       <c r="D77" t="s">
-        <v>982</v>
+        <v>967</v>
       </c>
       <c r="E77" t="s">
-        <v>540</v>
+        <v>534</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="H77" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="I77" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="J77" s="4" t="s">
         <v>213</v>
-      </c>
-      <c r="I77" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="J77" s="4" t="s">
-        <v>215</v>
       </c>
       <c r="K77" s="4"/>
       <c r="L77" s="4"/>
@@ -13040,7 +13040,7 @@
       <c r="AN77" s="4"/>
       <c r="AO77" s="4"/>
       <c r="AP77" s="4" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="AQ77" s="4"/>
       <c r="AR77" s="4"/>
@@ -13055,22 +13055,22 @@
     </row>
     <row r="78" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="4" t="s">
-        <v>544</v>
+        <v>538</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="C78" s="4">
         <v>77</v>
       </c>
       <c r="D78" t="s">
-        <v>984</v>
+        <v>969</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>546</v>
+        <v>540</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="H78" s="4" t="s">
         <v>71</v>
@@ -13079,7 +13079,7 @@
         <v>129</v>
       </c>
       <c r="J78" s="4" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="K78" s="4" t="b">
         <v>1</v>
@@ -13141,7 +13141,7 @@
       <c r="AN78" s="4"/>
       <c r="AO78" s="4"/>
       <c r="AP78" s="4" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="AQ78" s="4"/>
       <c r="AR78" s="4"/>
@@ -13162,25 +13162,25 @@
     </row>
     <row r="79" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="4" t="s">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>550</v>
+        <v>544</v>
       </c>
       <c r="C79" s="4">
         <v>78</v>
       </c>
       <c r="D79" t="s">
-        <v>985</v>
+        <v>970</v>
       </c>
       <c r="E79" t="s">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>553</v>
+        <v>547</v>
       </c>
       <c r="H79" s="4" t="s">
         <v>71</v>
@@ -13245,7 +13245,7 @@
       <c r="AN79" s="4"/>
       <c r="AO79" s="4"/>
       <c r="AP79" s="4" t="s">
-        <v>554</v>
+        <v>1066</v>
       </c>
       <c r="AQ79" s="4"/>
       <c r="AR79" s="4" t="s">
@@ -13262,25 +13262,25 @@
     </row>
     <row r="80" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="4" t="s">
-        <v>555</v>
+        <v>548</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>556</v>
+        <v>549</v>
       </c>
       <c r="C80" s="4">
         <v>79</v>
       </c>
       <c r="D80" t="s">
-        <v>986</v>
+        <v>971</v>
       </c>
       <c r="E80" t="s">
-        <v>557</v>
+        <v>550</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>558</v>
+        <v>551</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>559</v>
+        <v>552</v>
       </c>
       <c r="H80" s="4" t="s">
         <v>71</v>
@@ -13345,10 +13345,10 @@
       <c r="AN80" s="4"/>
       <c r="AO80" s="4"/>
       <c r="AP80" s="4" t="s">
-        <v>560</v>
+        <v>553</v>
       </c>
       <c r="AQ80" s="4" t="s">
-        <v>561</v>
+        <v>554</v>
       </c>
       <c r="AR80" s="4" t="s">
         <v>59</v>
@@ -13368,31 +13368,31 @@
     </row>
     <row r="81" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="4" t="s">
-        <v>562</v>
+        <v>555</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>563</v>
+        <v>556</v>
       </c>
       <c r="C81" s="4">
         <v>80</v>
       </c>
       <c r="D81" t="s">
-        <v>1024</v>
+        <v>1009</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>564</v>
+        <v>557</v>
       </c>
       <c r="G81" s="20" t="s">
-        <v>565</v>
+        <v>558</v>
       </c>
       <c r="H81" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I81" s="4" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="J81" s="4" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="K81" s="4"/>
       <c r="L81" s="4"/>
@@ -13428,7 +13428,7 @@
         <v>1</v>
       </c>
       <c r="AF81" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AG81" s="4"/>
       <c r="AH81" s="4"/>
@@ -13445,10 +13445,10 @@
       <c r="AN81" s="4"/>
       <c r="AO81" s="4"/>
       <c r="AP81" s="4" t="s">
-        <v>566</v>
+        <v>559</v>
       </c>
       <c r="AQ81" s="4" t="s">
-        <v>567</v>
+        <v>560</v>
       </c>
       <c r="AR81" s="4"/>
       <c r="AS81" s="4"/>
@@ -13464,34 +13464,34 @@
     </row>
     <row r="82" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="4" t="s">
-        <v>568</v>
+        <v>561</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>568</v>
+        <v>561</v>
       </c>
       <c r="C82" s="4">
         <v>81</v>
       </c>
       <c r="D82" t="s">
-        <v>987</v>
+        <v>972</v>
       </c>
       <c r="E82" t="s">
-        <v>569</v>
+        <v>562</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>570</v>
+        <v>563</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>571</v>
+        <v>564</v>
       </c>
       <c r="H82" s="4" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I82" s="4" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="J82" s="4" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="K82" s="4"/>
       <c r="L82" s="4"/>
@@ -13545,7 +13545,7 @@
       </c>
       <c r="AO82" s="4"/>
       <c r="AP82" s="4" t="s">
-        <v>572</v>
+        <v>565</v>
       </c>
       <c r="AQ82" s="4"/>
       <c r="AR82" s="4"/>
@@ -13560,34 +13560,34 @@
     </row>
     <row r="83" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="4" t="s">
-        <v>573</v>
+        <v>566</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>574</v>
+        <v>567</v>
       </c>
       <c r="C83" s="4">
         <v>82</v>
       </c>
       <c r="D83" t="s">
-        <v>988</v>
+        <v>973</v>
       </c>
       <c r="E83" t="s">
-        <v>575</v>
+        <v>568</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>576</v>
+        <v>569</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>577</v>
+        <v>570</v>
       </c>
       <c r="H83" s="4" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I83" s="4" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="J83" s="4" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="K83" s="4"/>
       <c r="L83" s="4"/>
@@ -13649,7 +13649,7 @@
         <v>59</v>
       </c>
       <c r="AP83" s="4" t="s">
-        <v>578</v>
+        <v>571</v>
       </c>
       <c r="AQ83" s="4"/>
       <c r="AR83" s="4"/>
@@ -13664,34 +13664,34 @@
     </row>
     <row r="84" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="4" t="s">
-        <v>579</v>
+        <v>572</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>580</v>
+        <v>573</v>
       </c>
       <c r="C84" s="4">
         <v>83</v>
       </c>
       <c r="D84" t="s">
-        <v>989</v>
+        <v>974</v>
       </c>
       <c r="E84" t="s">
-        <v>581</v>
+        <v>574</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>582</v>
+        <v>575</v>
       </c>
       <c r="G84" s="4" t="s">
-        <v>583</v>
+        <v>576</v>
       </c>
       <c r="H84" s="4" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I84" s="4" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="J84" s="4" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="K84" s="4"/>
       <c r="L84" s="4"/>
@@ -13751,7 +13751,7 @@
       <c r="AN84" s="4"/>
       <c r="AO84" s="4"/>
       <c r="AP84" s="4" t="s">
-        <v>584</v>
+        <v>1067</v>
       </c>
       <c r="AQ84" s="4"/>
       <c r="AR84" s="4"/>
@@ -13766,21 +13766,21 @@
     </row>
     <row r="85" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="4" t="s">
-        <v>585</v>
+        <v>577</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>586</v>
+        <v>578</v>
       </c>
       <c r="C85" s="4">
         <v>84</v>
       </c>
       <c r="D85" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="F85" s="4"/>
       <c r="G85" s="4"/>
       <c r="H85" s="4" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="I85" s="4"/>
       <c r="J85" s="4"/>
@@ -13791,19 +13791,19 @@
       <c r="O85" s="4"/>
       <c r="P85" s="4"/>
       <c r="Q85" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="R85" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="S85" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="T85" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="U85" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="V85" s="4"/>
       <c r="W85" s="4"/>
@@ -13815,10 +13815,10 @@
       <c r="AC85" s="4"/>
       <c r="AD85" s="4"/>
       <c r="AE85" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AF85" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AG85" s="4"/>
       <c r="AH85" s="4"/>
@@ -13833,7 +13833,7 @@
       <c r="AN85" s="4"/>
       <c r="AO85" s="4"/>
       <c r="AP85" s="4" t="s">
-        <v>587</v>
+        <v>579</v>
       </c>
       <c r="AQ85" s="4"/>
       <c r="AR85" s="4"/>
@@ -13850,34 +13850,34 @@
     </row>
     <row r="86" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="4" t="s">
-        <v>588</v>
+        <v>580</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>589</v>
+        <v>581</v>
       </c>
       <c r="C86" s="4">
         <v>85</v>
       </c>
       <c r="D86" t="s">
-        <v>990</v>
+        <v>975</v>
       </c>
       <c r="E86" t="s">
-        <v>590</v>
+        <v>582</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>591</v>
+        <v>583</v>
       </c>
       <c r="G86" s="4" t="s">
-        <v>592</v>
+        <v>584</v>
       </c>
       <c r="H86" s="4" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I86" s="4" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="J86" s="4" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="K86" s="4"/>
       <c r="L86" s="4"/>
@@ -13928,10 +13928,10 @@
       </c>
       <c r="AN86" s="4"/>
       <c r="AO86" s="4" t="s">
-        <v>593</v>
+        <v>585</v>
       </c>
       <c r="AP86" s="4" t="s">
-        <v>594</v>
+        <v>1068</v>
       </c>
       <c r="AQ86" s="4"/>
       <c r="AR86" s="4"/>
@@ -13946,34 +13946,34 @@
     </row>
     <row r="87" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="4" t="s">
-        <v>595</v>
+        <v>586</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>596</v>
+        <v>587</v>
       </c>
       <c r="C87" s="4">
         <v>86</v>
       </c>
       <c r="D87" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="E87" t="s">
-        <v>597</v>
+        <v>588</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>598</v>
+        <v>589</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>599</v>
+        <v>590</v>
       </c>
       <c r="H87" s="4" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I87" s="4" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="J87" s="4" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="K87" s="4"/>
       <c r="L87" s="4"/>
@@ -14033,7 +14033,7 @@
         <v>59</v>
       </c>
       <c r="AP87" s="4" t="s">
-        <v>600</v>
+        <v>591</v>
       </c>
       <c r="AQ87" s="4"/>
       <c r="AR87" s="4"/>
@@ -14048,34 +14048,34 @@
     </row>
     <row r="88" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="4" t="s">
-        <v>601</v>
+        <v>592</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>602</v>
+        <v>593</v>
       </c>
       <c r="C88" s="4">
         <v>87</v>
       </c>
       <c r="D88" t="s">
-        <v>991</v>
+        <v>976</v>
       </c>
       <c r="E88" t="s">
-        <v>603</v>
+        <v>594</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>604</v>
+        <v>595</v>
       </c>
       <c r="G88" s="4" t="s">
-        <v>605</v>
+        <v>596</v>
       </c>
       <c r="H88" s="4" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I88" s="4" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="J88" s="4" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="K88" s="4"/>
       <c r="L88" s="4"/>
@@ -14083,7 +14083,7 @@
       <c r="N88" s="4"/>
       <c r="O88" s="4"/>
       <c r="P88" s="4" t="s">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="Q88">
         <v>5</v>
@@ -14135,11 +14135,11 @@
       <c r="AN88" s="4"/>
       <c r="AO88" s="4"/>
       <c r="AP88" s="4" t="s">
-        <v>606</v>
+        <v>597</v>
       </c>
       <c r="AQ88" s="4"/>
       <c r="AR88" s="4" t="s">
-        <v>1038</v>
+        <v>1023</v>
       </c>
       <c r="AS88" s="4" t="b">
         <v>1</v>
@@ -14152,34 +14152,34 @@
     </row>
     <row r="89" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="4" t="s">
-        <v>607</v>
+        <v>598</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>608</v>
+        <v>599</v>
       </c>
       <c r="C89" s="4">
         <v>88</v>
       </c>
       <c r="D89" t="s">
-        <v>992</v>
+        <v>977</v>
       </c>
       <c r="E89" t="s">
-        <v>609</v>
+        <v>600</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>610</v>
+        <v>601</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>611</v>
+        <v>602</v>
       </c>
       <c r="H89" s="4" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I89" s="4" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="J89" s="4" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="K89" s="4"/>
       <c r="L89" s="4"/>
@@ -14233,7 +14233,7 @@
       <c r="AN89" s="4"/>
       <c r="AO89" s="4"/>
       <c r="AP89" s="4" t="s">
-        <v>612</v>
+        <v>603</v>
       </c>
       <c r="AQ89" s="4"/>
       <c r="AR89" s="4"/>
@@ -14248,25 +14248,25 @@
     </row>
     <row r="90" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="4" t="s">
-        <v>613</v>
+        <v>604</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>614</v>
+        <v>605</v>
       </c>
       <c r="C90" s="4">
         <v>89</v>
       </c>
       <c r="D90" t="s">
-        <v>950</v>
+        <v>935</v>
       </c>
       <c r="E90" t="s">
-        <v>615</v>
+        <v>606</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>616</v>
+        <v>607</v>
       </c>
       <c r="G90" s="4" t="s">
-        <v>617</v>
+        <v>608</v>
       </c>
       <c r="H90" s="4" t="s">
         <v>71</v>
@@ -14329,7 +14329,7 @@
       <c r="AN90" s="4"/>
       <c r="AO90" s="4"/>
       <c r="AP90" s="4" t="s">
-        <v>618</v>
+        <v>1069</v>
       </c>
       <c r="AQ90" s="4"/>
       <c r="AR90" s="4" t="s">
@@ -14350,31 +14350,31 @@
     </row>
     <row r="91" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="4" t="s">
-        <v>619</v>
+        <v>609</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>620</v>
+        <v>610</v>
       </c>
       <c r="C91" s="4">
         <v>90</v>
       </c>
       <c r="D91" t="s">
-        <v>1025</v>
+        <v>1010</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>621</v>
+        <v>611</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
       <c r="H91" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I91" s="4" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="J91" s="4" t="s">
-        <v>623</v>
+        <v>613</v>
       </c>
       <c r="K91" s="4"/>
       <c r="L91" s="4"/>
@@ -14410,7 +14410,7 @@
         <v>0</v>
       </c>
       <c r="AF91" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AG91" s="4"/>
       <c r="AH91" s="4"/>
@@ -14427,7 +14427,7 @@
       <c r="AN91" s="4"/>
       <c r="AO91" s="4"/>
       <c r="AP91" s="4" t="s">
-        <v>624</v>
+        <v>614</v>
       </c>
       <c r="AQ91" s="4"/>
       <c r="AR91" s="4" t="s">
@@ -14446,25 +14446,25 @@
     </row>
     <row r="92" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="4" t="s">
-        <v>625</v>
+        <v>615</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>626</v>
+        <v>616</v>
       </c>
       <c r="C92" s="4">
         <v>91</v>
       </c>
       <c r="D92" t="s">
-        <v>961</v>
+        <v>946</v>
       </c>
       <c r="E92" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
       <c r="G92" s="4" t="s">
-        <v>629</v>
+        <v>619</v>
       </c>
       <c r="H92" s="4" t="s">
         <v>71</v>
@@ -14473,7 +14473,7 @@
         <v>129</v>
       </c>
       <c r="J92" s="4" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="K92" s="4" t="b">
         <v>1</v>
@@ -14527,7 +14527,7 @@
       <c r="AN92" s="4"/>
       <c r="AO92" s="4"/>
       <c r="AP92" s="4" t="s">
-        <v>630</v>
+        <v>1070</v>
       </c>
       <c r="AQ92" s="4"/>
       <c r="AR92" s="4"/>
@@ -14542,31 +14542,31 @@
     </row>
     <row r="93" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="4" t="s">
-        <v>631</v>
+        <v>620</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>632</v>
+        <v>621</v>
       </c>
       <c r="C93" s="4">
         <v>92</v>
       </c>
       <c r="D93" t="s">
-        <v>993</v>
+        <v>978</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>633</v>
+        <v>622</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>634</v>
+        <v>623</v>
       </c>
       <c r="H93" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I93" s="4" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="J93" s="4" t="s">
-        <v>635</v>
+        <v>624</v>
       </c>
       <c r="K93" s="4"/>
       <c r="L93" s="4"/>
@@ -14605,19 +14605,19 @@
         <v>0</v>
       </c>
       <c r="AF93" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AG93" s="4">
         <v>0</v>
       </c>
       <c r="AH93" s="4"/>
       <c r="AI93" s="4" t="s">
-        <v>636</v>
+        <v>625</v>
       </c>
       <c r="AJ93" s="4"/>
       <c r="AK93" s="4"/>
       <c r="AL93" s="4" t="s">
-        <v>637</v>
+        <v>626</v>
       </c>
       <c r="AM93" s="4" t="b">
         <f t="shared" si="2"/>
@@ -14626,7 +14626,7 @@
       <c r="AN93" s="4"/>
       <c r="AO93" s="4"/>
       <c r="AP93" s="4" t="s">
-        <v>638</v>
+        <v>627</v>
       </c>
       <c r="AQ93" s="4"/>
       <c r="AR93" s="4" t="s">
@@ -14649,31 +14649,31 @@
     </row>
     <row r="94" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="4" t="s">
-        <v>639</v>
+        <v>628</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>640</v>
+        <v>629</v>
       </c>
       <c r="C94" s="4">
         <v>93</v>
       </c>
       <c r="D94" t="s">
-        <v>1026</v>
+        <v>1011</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>641</v>
+        <v>630</v>
       </c>
       <c r="G94" s="20" t="s">
-        <v>642</v>
+        <v>631</v>
       </c>
       <c r="H94" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I94" s="4" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="J94" s="4" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="K94" s="4"/>
       <c r="L94" s="4"/>
@@ -14709,7 +14709,7 @@
         <v>0</v>
       </c>
       <c r="AF94" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AG94" s="4"/>
       <c r="AH94" s="4"/>
@@ -14724,7 +14724,7 @@
       <c r="AN94" s="4"/>
       <c r="AO94" s="4"/>
       <c r="AP94" s="4" t="s">
-        <v>643</v>
+        <v>632</v>
       </c>
       <c r="AQ94" s="4"/>
       <c r="AR94" s="4" t="s">
@@ -14743,27 +14743,27 @@
     </row>
     <row r="95" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="4" t="s">
-        <v>644</v>
+        <v>633</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>645</v>
+        <v>634</v>
       </c>
       <c r="C95" s="4">
         <v>94</v>
       </c>
       <c r="D95" t="s">
-        <v>1027</v>
+        <v>1012</v>
       </c>
       <c r="F95" s="4"/>
       <c r="G95" s="4"/>
       <c r="H95" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I95" s="4" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="J95" s="4" t="s">
-        <v>646</v>
+        <v>635</v>
       </c>
       <c r="K95" s="4"/>
       <c r="L95" s="4"/>
@@ -14799,7 +14799,7 @@
         <v>0</v>
       </c>
       <c r="AF95" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AG95" s="4"/>
       <c r="AH95" s="4"/>
@@ -14816,7 +14816,7 @@
       <c r="AN95" s="4"/>
       <c r="AO95" s="4"/>
       <c r="AP95" s="4" t="s">
-        <v>647</v>
+        <v>636</v>
       </c>
       <c r="AQ95" s="4"/>
       <c r="AR95" s="4" t="s">
@@ -14835,31 +14835,31 @@
     </row>
     <row r="96" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="4" t="s">
-        <v>648</v>
+        <v>637</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>649</v>
+        <v>638</v>
       </c>
       <c r="C96" s="4">
         <v>95</v>
       </c>
       <c r="D96" t="s">
-        <v>994</v>
+        <v>979</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>650</v>
+        <v>639</v>
       </c>
       <c r="G96" s="4" t="s">
-        <v>651</v>
+        <v>640</v>
       </c>
       <c r="H96" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I96" s="4" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="J96" s="4" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="K96" s="4"/>
       <c r="L96" s="4"/>
@@ -14896,7 +14896,7 @@
         <v>0</v>
       </c>
       <c r="AF96" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AG96" s="4">
         <v>2E-3</v>
@@ -14905,7 +14905,7 @@
         <v>2E-3</v>
       </c>
       <c r="AI96" s="4" t="s">
-        <v>652</v>
+        <v>641</v>
       </c>
       <c r="AJ96" s="4"/>
       <c r="AK96" s="4"/>
@@ -14919,7 +14919,7 @@
       <c r="AN96" s="4"/>
       <c r="AO96" s="4"/>
       <c r="AP96" s="4" t="s">
-        <v>653</v>
+        <v>642</v>
       </c>
       <c r="AQ96" s="4"/>
       <c r="AR96" s="4" t="s">
@@ -14942,25 +14942,25 @@
     </row>
     <row r="97" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="4" t="s">
-        <v>654</v>
+        <v>643</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>655</v>
+        <v>644</v>
       </c>
       <c r="C97" s="4">
         <v>96</v>
       </c>
       <c r="D97" t="s">
-        <v>995</v>
+        <v>980</v>
       </c>
       <c r="E97" t="s">
-        <v>656</v>
+        <v>645</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>657</v>
+        <v>646</v>
       </c>
       <c r="G97" s="4" t="s">
-        <v>658</v>
+        <v>647</v>
       </c>
       <c r="H97" s="4" t="s">
         <v>71</v>
@@ -15031,7 +15031,7 @@
         <v>59</v>
       </c>
       <c r="AP97" s="4" t="s">
-        <v>659</v>
+        <v>648</v>
       </c>
       <c r="AQ97" s="4"/>
       <c r="AR97" s="4"/>
@@ -15046,34 +15046,34 @@
     </row>
     <row r="98" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="4" t="s">
-        <v>660</v>
+        <v>649</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>661</v>
+        <v>650</v>
       </c>
       <c r="C98" s="4">
         <v>97</v>
       </c>
       <c r="D98" t="s">
-        <v>996</v>
+        <v>981</v>
       </c>
       <c r="E98" t="s">
-        <v>662</v>
+        <v>651</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>663</v>
+        <v>652</v>
       </c>
       <c r="G98" s="4" t="s">
-        <v>664</v>
+        <v>653</v>
       </c>
       <c r="H98" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="I98" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="J98" s="4" t="s">
         <v>213</v>
-      </c>
-      <c r="I98" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="J98" s="4" t="s">
-        <v>215</v>
       </c>
       <c r="K98" s="4"/>
       <c r="L98" s="4"/>
@@ -15129,7 +15129,7 @@
       <c r="AN98" s="4"/>
       <c r="AO98" s="4"/>
       <c r="AP98" s="4" t="s">
-        <v>665</v>
+        <v>654</v>
       </c>
       <c r="AQ98" s="4"/>
       <c r="AR98" s="4"/>
@@ -15144,34 +15144,34 @@
     </row>
     <row r="99" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="4" t="s">
-        <v>666</v>
+        <v>655</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>667</v>
+        <v>656</v>
       </c>
       <c r="C99" s="4">
         <v>98</v>
       </c>
       <c r="D99" t="s">
-        <v>992</v>
+        <v>977</v>
       </c>
       <c r="E99" t="s">
-        <v>668</v>
+        <v>657</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>669</v>
+        <v>658</v>
       </c>
       <c r="G99" s="4" t="s">
-        <v>670</v>
+        <v>659</v>
       </c>
       <c r="H99" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="I99" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="J99" s="4" t="s">
         <v>213</v>
-      </c>
-      <c r="I99" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="J99" s="4" t="s">
-        <v>215</v>
       </c>
       <c r="K99" s="4"/>
       <c r="L99" s="4"/>
@@ -15225,7 +15225,7 @@
       <c r="AN99" s="4"/>
       <c r="AO99" s="4"/>
       <c r="AP99" s="4" t="s">
-        <v>671</v>
+        <v>1071</v>
       </c>
       <c r="AQ99" s="4"/>
       <c r="AR99" s="4"/>
@@ -15240,34 +15240,34 @@
     </row>
     <row r="100" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="4" t="s">
-        <v>672</v>
+        <v>660</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>673</v>
+        <v>661</v>
       </c>
       <c r="C100" s="4">
         <v>99</v>
       </c>
       <c r="D100" t="s">
-        <v>997</v>
+        <v>982</v>
       </c>
       <c r="E100" t="s">
-        <v>674</v>
+        <v>662</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>675</v>
+        <v>663</v>
       </c>
       <c r="G100" s="4" t="s">
-        <v>676</v>
+        <v>664</v>
       </c>
       <c r="H100" s="4" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I100" s="4" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="J100" s="4" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="K100" s="4"/>
       <c r="L100" s="4"/>
@@ -15323,7 +15323,7 @@
       <c r="AN100" s="4"/>
       <c r="AO100" s="4"/>
       <c r="AP100" s="4" t="s">
-        <v>677</v>
+        <v>665</v>
       </c>
       <c r="AQ100" s="4"/>
       <c r="AR100" s="4"/>
@@ -15342,25 +15342,25 @@
     </row>
     <row r="101" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="4" t="s">
-        <v>678</v>
+        <v>666</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>679</v>
+        <v>667</v>
       </c>
       <c r="C101" s="4">
         <v>100</v>
       </c>
       <c r="D101" t="s">
-        <v>998</v>
+        <v>983</v>
       </c>
       <c r="E101" t="s">
-        <v>680</v>
+        <v>668</v>
       </c>
       <c r="F101" s="4" t="s">
-        <v>681</v>
+        <v>669</v>
       </c>
       <c r="G101" s="4" t="s">
-        <v>682</v>
+        <v>670</v>
       </c>
       <c r="H101" s="4" t="s">
         <v>71</v>
@@ -15429,7 +15429,7 @@
       <c r="AN101" s="4"/>
       <c r="AO101" s="4"/>
       <c r="AP101" s="4" t="s">
-        <v>683</v>
+        <v>671</v>
       </c>
       <c r="AQ101" s="4"/>
       <c r="AR101" s="4"/>
@@ -15450,25 +15450,25 @@
     </row>
     <row r="102" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="4" t="s">
-        <v>684</v>
+        <v>672</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>685</v>
+        <v>673</v>
       </c>
       <c r="C102" s="4">
         <v>101</v>
       </c>
       <c r="D102" t="s">
-        <v>998</v>
+        <v>983</v>
       </c>
       <c r="E102" s="24" t="s">
-        <v>686</v>
+        <v>674</v>
       </c>
       <c r="F102" s="4" t="s">
-        <v>687</v>
+        <v>675</v>
       </c>
       <c r="G102" s="4" t="s">
-        <v>688</v>
+        <v>676</v>
       </c>
       <c r="H102" s="4" t="s">
         <v>71</v>
@@ -15537,7 +15537,7 @@
       <c r="AN102" s="4"/>
       <c r="AO102" s="4"/>
       <c r="AP102" s="4" t="s">
-        <v>689</v>
+        <v>677</v>
       </c>
       <c r="AQ102" s="4"/>
       <c r="AR102" s="4"/>
@@ -15558,27 +15558,27 @@
     </row>
     <row r="103" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="4" t="s">
-        <v>690</v>
+        <v>678</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>691</v>
+        <v>679</v>
       </c>
       <c r="C103" s="4">
         <v>102</v>
       </c>
       <c r="D103" t="s">
-        <v>1028</v>
+        <v>1013</v>
       </c>
       <c r="F103" s="4"/>
       <c r="G103" s="4"/>
       <c r="H103" s="4" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I103" s="4" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="J103" s="4" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="K103" s="4"/>
       <c r="L103" s="4"/>
@@ -15631,7 +15631,7 @@
       <c r="AN103" s="4"/>
       <c r="AO103" s="4"/>
       <c r="AP103" s="4" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="AQ103" s="4"/>
       <c r="AR103" s="4"/>
@@ -15646,27 +15646,27 @@
     </row>
     <row r="104" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="4" t="s">
-        <v>692</v>
+        <v>680</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>693</v>
+        <v>681</v>
       </c>
       <c r="C104" s="4">
         <v>103</v>
       </c>
       <c r="D104" t="s">
-        <v>1029</v>
+        <v>1014</v>
       </c>
       <c r="F104" s="4"/>
       <c r="G104" s="4"/>
       <c r="H104" s="4" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I104" s="4" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="J104" s="4" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="K104" s="4"/>
       <c r="L104" s="4"/>
@@ -15719,7 +15719,7 @@
       <c r="AN104" s="4"/>
       <c r="AO104" s="4"/>
       <c r="AP104" s="4" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="AQ104" s="4"/>
       <c r="AR104" s="4"/>
@@ -15734,22 +15734,22 @@
     </row>
     <row r="105" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="4" t="s">
-        <v>694</v>
+        <v>682</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>695</v>
+        <v>683</v>
       </c>
       <c r="C105" s="4">
         <v>104</v>
       </c>
       <c r="D105" t="s">
-        <v>999</v>
+        <v>984</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>696</v>
+        <v>684</v>
       </c>
       <c r="G105" s="4" t="s">
-        <v>697</v>
+        <v>685</v>
       </c>
       <c r="H105" s="4" t="s">
         <v>71</v>
@@ -15758,7 +15758,7 @@
         <v>75</v>
       </c>
       <c r="J105" s="4" t="s">
-        <v>694</v>
+        <v>682</v>
       </c>
       <c r="K105" s="4" t="b">
         <v>1</v>
@@ -15818,7 +15818,7 @@
       <c r="AN105" s="4"/>
       <c r="AO105" s="4"/>
       <c r="AP105" s="4" t="s">
-        <v>698</v>
+        <v>686</v>
       </c>
       <c r="AQ105" s="4"/>
       <c r="AR105" s="4"/>
@@ -15839,31 +15839,31 @@
     </row>
     <row r="106" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="4" t="s">
-        <v>699</v>
+        <v>687</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>700</v>
+        <v>688</v>
       </c>
       <c r="C106" s="4">
         <v>105</v>
       </c>
       <c r="D106" t="s">
-        <v>1000</v>
+        <v>985</v>
       </c>
       <c r="F106" s="4" t="s">
-        <v>701</v>
+        <v>689</v>
       </c>
       <c r="G106" s="4" t="s">
-        <v>702</v>
+        <v>690</v>
       </c>
       <c r="H106" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I106" s="4" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="J106" s="4" t="s">
-        <v>703</v>
+        <v>691</v>
       </c>
       <c r="K106" s="4"/>
       <c r="L106" s="4"/>
@@ -15902,7 +15902,7 @@
         <v>1</v>
       </c>
       <c r="AF106" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AG106" s="4"/>
       <c r="AH106" s="4"/>
@@ -15917,7 +15917,7 @@
       <c r="AN106" s="4"/>
       <c r="AO106" s="4"/>
       <c r="AP106" s="4" t="s">
-        <v>704</v>
+        <v>1072</v>
       </c>
       <c r="AQ106" s="4"/>
       <c r="AR106" s="4" t="s">
@@ -15934,31 +15934,31 @@
     </row>
     <row r="107" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="4" t="s">
-        <v>705</v>
+        <v>692</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>706</v>
+        <v>693</v>
       </c>
       <c r="C107" s="4">
         <v>106</v>
       </c>
       <c r="D107" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="F107" s="4" t="s">
-        <v>707</v>
+        <v>694</v>
       </c>
       <c r="G107" s="4" t="s">
-        <v>708</v>
+        <v>695</v>
       </c>
       <c r="H107" s="4" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I107" s="4" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="J107" s="4" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="K107" s="4"/>
       <c r="L107" s="4"/>
@@ -16006,7 +16006,7 @@
         <v>2E-3</v>
       </c>
       <c r="AI107" s="4" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="AJ107" s="4"/>
       <c r="AK107" s="4"/>
@@ -16018,7 +16018,7 @@
       <c r="AN107" s="4"/>
       <c r="AO107" s="4"/>
       <c r="AP107" s="4" t="s">
-        <v>709</v>
+        <v>696</v>
       </c>
       <c r="AQ107" s="4"/>
       <c r="AR107" s="4"/>
@@ -16033,31 +16033,31 @@
     </row>
     <row r="108" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="4" t="s">
-        <v>710</v>
+        <v>697</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>711</v>
+        <v>698</v>
       </c>
       <c r="C108" s="4">
         <v>107</v>
       </c>
       <c r="D108" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="F108" s="4" t="s">
-        <v>712</v>
+        <v>699</v>
       </c>
       <c r="G108" s="4" t="s">
-        <v>708</v>
+        <v>695</v>
       </c>
       <c r="H108" s="4" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I108" s="4" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="J108" s="4" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="K108" s="4"/>
       <c r="L108" s="4"/>
@@ -16105,7 +16105,7 @@
         <v>2E-3</v>
       </c>
       <c r="AI108" s="4" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="AJ108" s="4"/>
       <c r="AK108" s="4"/>
@@ -16117,7 +16117,7 @@
       <c r="AN108" s="4"/>
       <c r="AO108" s="4"/>
       <c r="AP108" s="4" t="s">
-        <v>713</v>
+        <v>700</v>
       </c>
       <c r="AQ108" s="4"/>
       <c r="AR108" s="4"/>
@@ -16132,22 +16132,22 @@
     </row>
     <row r="109" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="4" t="s">
-        <v>714</v>
+        <v>701</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="C109" s="4">
         <v>108</v>
       </c>
       <c r="D109" t="s">
-        <v>1001</v>
+        <v>986</v>
       </c>
       <c r="F109" s="4" t="s">
-        <v>716</v>
+        <v>703</v>
       </c>
       <c r="G109" s="4" t="s">
-        <v>717</v>
+        <v>704</v>
       </c>
       <c r="H109" s="4" t="s">
         <v>71</v>
@@ -16222,7 +16222,7 @@
         <v>59</v>
       </c>
       <c r="AP109" s="4" t="s">
-        <v>718</v>
+        <v>705</v>
       </c>
       <c r="AQ109" s="4"/>
       <c r="AR109" s="4"/>
@@ -16237,21 +16237,21 @@
     </row>
     <row r="110" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="4" t="s">
-        <v>719</v>
+        <v>706</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>719</v>
+        <v>706</v>
       </c>
       <c r="C110" s="4">
         <v>109</v>
       </c>
       <c r="D110" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="F110" s="4"/>
       <c r="G110" s="4"/>
       <c r="H110" s="4" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="I110" s="4"/>
       <c r="J110" s="4"/>
@@ -16262,19 +16262,19 @@
       <c r="O110" s="4"/>
       <c r="P110" s="4"/>
       <c r="Q110" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="R110" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="S110" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="T110" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="U110" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="V110" s="4"/>
       <c r="W110" s="4"/>
@@ -16286,16 +16286,16 @@
       <c r="AC110" s="4"/>
       <c r="AD110" s="4"/>
       <c r="AE110" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AF110" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AG110" s="4"/>
       <c r="AH110" s="4"/>
       <c r="AI110" s="4"/>
       <c r="AJ110" s="4" t="s">
-        <v>720</v>
+        <v>707</v>
       </c>
       <c r="AK110" s="4"/>
       <c r="AL110" s="4"/>
@@ -16306,7 +16306,7 @@
       <c r="AN110" s="4"/>
       <c r="AO110" s="4"/>
       <c r="AP110" s="4" t="s">
-        <v>721</v>
+        <v>708</v>
       </c>
       <c r="AQ110" s="4"/>
       <c r="AR110" s="4"/>
@@ -16321,22 +16321,22 @@
     </row>
     <row r="111" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="4" t="s">
-        <v>722</v>
+        <v>709</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>723</v>
+        <v>710</v>
       </c>
       <c r="C111" s="4">
         <v>110</v>
       </c>
       <c r="D111" t="s">
-        <v>942</v>
+        <v>927</v>
       </c>
       <c r="F111" s="4" t="s">
-        <v>724</v>
+        <v>711</v>
       </c>
       <c r="G111" s="4" t="s">
-        <v>725</v>
+        <v>712</v>
       </c>
       <c r="H111" s="4" t="s">
         <v>71</v>
@@ -16401,7 +16401,7 @@
       <c r="AN111" s="4"/>
       <c r="AO111" s="4"/>
       <c r="AP111" s="4" t="s">
-        <v>726</v>
+        <v>713</v>
       </c>
       <c r="AQ111" s="4"/>
       <c r="AR111" s="4" t="s">
@@ -16422,28 +16422,28 @@
     </row>
     <row r="112" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="4" t="s">
-        <v>727</v>
+        <v>714</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>728</v>
+        <v>715</v>
       </c>
       <c r="C112" s="4">
         <v>111</v>
       </c>
       <c r="D112" t="s">
-        <v>1030</v>
+        <v>1015</v>
       </c>
       <c r="E112" s="24" t="s">
-        <v>729</v>
+        <v>716</v>
       </c>
       <c r="F112" s="4" t="s">
-        <v>730</v>
+        <v>717</v>
       </c>
       <c r="G112" s="20" t="s">
-        <v>731</v>
+        <v>718</v>
       </c>
       <c r="H112" s="4" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="I112" s="4"/>
       <c r="J112" s="4"/>
@@ -16492,7 +16492,7 @@
       <c r="AN112" s="4"/>
       <c r="AO112" s="4"/>
       <c r="AP112" s="4" t="s">
-        <v>732</v>
+        <v>719</v>
       </c>
       <c r="AQ112" s="4"/>
       <c r="AR112" s="4"/>
@@ -16509,31 +16509,31 @@
     </row>
     <row r="113" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="4" t="s">
-        <v>733</v>
+        <v>720</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>734</v>
+        <v>721</v>
       </c>
       <c r="C113" s="4">
         <v>112</v>
       </c>
       <c r="D113" t="s">
-        <v>1031</v>
+        <v>1016</v>
       </c>
       <c r="F113" s="4" t="s">
-        <v>735</v>
+        <v>722</v>
       </c>
       <c r="G113" s="20" t="s">
-        <v>736</v>
+        <v>723</v>
       </c>
       <c r="H113" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I113" s="4" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="J113" s="4" t="s">
-        <v>737</v>
+        <v>724</v>
       </c>
       <c r="K113" s="4"/>
       <c r="L113" s="4"/>
@@ -16569,7 +16569,7 @@
         <v>0</v>
       </c>
       <c r="AF113" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AG113" s="4"/>
       <c r="AH113" s="4"/>
@@ -16584,7 +16584,7 @@
       <c r="AN113" s="4"/>
       <c r="AO113" s="4"/>
       <c r="AP113" s="4" t="s">
-        <v>738</v>
+        <v>725</v>
       </c>
       <c r="AQ113" s="4"/>
       <c r="AR113" s="4"/>
@@ -16601,25 +16601,25 @@
     </row>
     <row r="114" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="4" t="s">
-        <v>739</v>
+        <v>726</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>740</v>
+        <v>727</v>
       </c>
       <c r="C114" s="4">
         <v>113</v>
       </c>
       <c r="D114" t="s">
-        <v>1002</v>
+        <v>987</v>
       </c>
       <c r="E114" t="s">
-        <v>741</v>
+        <v>728</v>
       </c>
       <c r="F114" s="4" t="s">
-        <v>742</v>
+        <v>729</v>
       </c>
       <c r="G114" s="4" t="s">
-        <v>743</v>
+        <v>730</v>
       </c>
       <c r="H114" s="4" t="s">
         <v>71</v>
@@ -16628,7 +16628,7 @@
         <v>129</v>
       </c>
       <c r="J114" s="4" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="K114" s="4" t="b">
         <v>1</v>
@@ -16682,7 +16682,7 @@
       <c r="AN114" s="4"/>
       <c r="AO114" s="4"/>
       <c r="AP114" s="4" t="s">
-        <v>744</v>
+        <v>731</v>
       </c>
       <c r="AQ114" s="4"/>
       <c r="AR114" s="4"/>
@@ -16701,25 +16701,25 @@
     </row>
     <row r="115" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="4" t="s">
-        <v>745</v>
+        <v>732</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>746</v>
+        <v>733</v>
       </c>
       <c r="C115" s="4">
         <v>114</v>
       </c>
       <c r="D115" t="s">
-        <v>1002</v>
+        <v>987</v>
       </c>
       <c r="E115" t="s">
-        <v>747</v>
+        <v>734</v>
       </c>
       <c r="F115" s="4" t="s">
-        <v>748</v>
+        <v>735</v>
       </c>
       <c r="G115" s="4" t="s">
-        <v>749</v>
+        <v>736</v>
       </c>
       <c r="H115" s="4" t="s">
         <v>71</v>
@@ -16728,7 +16728,7 @@
         <v>129</v>
       </c>
       <c r="J115" s="4" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="K115" s="4" t="b">
         <v>1</v>
@@ -16784,7 +16784,7 @@
       <c r="AN115" s="4"/>
       <c r="AO115" s="4"/>
       <c r="AP115" s="4" t="s">
-        <v>750</v>
+        <v>737</v>
       </c>
       <c r="AQ115" s="4"/>
       <c r="AR115" s="4"/>
@@ -16803,22 +16803,22 @@
     </row>
     <row r="116" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="4" t="s">
-        <v>751</v>
+        <v>738</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>752</v>
+        <v>739</v>
       </c>
       <c r="C116" s="4">
         <v>115</v>
       </c>
       <c r="D116" t="s">
-        <v>985</v>
+        <v>970</v>
       </c>
       <c r="F116" s="4" t="s">
-        <v>753</v>
+        <v>740</v>
       </c>
       <c r="G116" s="4" t="s">
-        <v>754</v>
+        <v>741</v>
       </c>
       <c r="H116" s="4" t="s">
         <v>71</v>
@@ -16881,7 +16881,7 @@
       <c r="AN116" s="4"/>
       <c r="AO116" s="4"/>
       <c r="AP116" s="4" t="s">
-        <v>755</v>
+        <v>742</v>
       </c>
       <c r="AQ116" s="4"/>
       <c r="AR116" s="4" t="s">
@@ -16902,31 +16902,31 @@
     </row>
     <row r="117" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="4" t="s">
-        <v>756</v>
+        <v>743</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>757</v>
+        <v>744</v>
       </c>
       <c r="C117" s="4">
         <v>116</v>
       </c>
       <c r="D117" t="s">
-        <v>1003</v>
+        <v>988</v>
       </c>
       <c r="F117" s="4" t="s">
-        <v>758</v>
+        <v>745</v>
       </c>
       <c r="G117" s="4" t="s">
-        <v>759</v>
+        <v>746</v>
       </c>
       <c r="H117" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I117" s="4" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="J117" s="4" t="s">
-        <v>760</v>
+        <v>747</v>
       </c>
       <c r="K117" s="4"/>
       <c r="L117" s="4"/>
@@ -16963,7 +16963,7 @@
         <v>0</v>
       </c>
       <c r="AF117" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AG117" s="4">
         <v>0.05</v>
@@ -16984,7 +16984,7 @@
       <c r="AN117" s="4"/>
       <c r="AO117" s="4"/>
       <c r="AP117" s="4" t="s">
-        <v>761</v>
+        <v>748</v>
       </c>
       <c r="AQ117" s="4"/>
       <c r="AR117" s="4" t="s">
@@ -17005,25 +17005,25 @@
     </row>
     <row r="118" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="4" t="s">
-        <v>762</v>
+        <v>749</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>763</v>
+        <v>750</v>
       </c>
       <c r="C118" s="4">
         <v>117</v>
       </c>
       <c r="D118" t="s">
-        <v>1032</v>
+        <v>1017</v>
       </c>
       <c r="F118" s="4" t="s">
-        <v>764</v>
+        <v>751</v>
       </c>
       <c r="G118" s="20" t="s">
-        <v>765</v>
+        <v>752</v>
       </c>
       <c r="H118" s="4" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="I118" s="4"/>
       <c r="J118" s="4"/>
@@ -17076,7 +17076,7 @@
       <c r="AN118" s="4"/>
       <c r="AO118" s="4"/>
       <c r="AP118" s="4" t="s">
-        <v>766</v>
+        <v>753</v>
       </c>
       <c r="AQ118" s="4"/>
       <c r="AR118" s="4"/>
@@ -17093,31 +17093,31 @@
     </row>
     <row r="119" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="4" t="s">
-        <v>767</v>
+        <v>754</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>768</v>
+        <v>755</v>
       </c>
       <c r="C119" s="4">
         <v>118</v>
       </c>
       <c r="D119" t="s">
-        <v>1004</v>
+        <v>989</v>
       </c>
       <c r="E119" t="s">
-        <v>769</v>
+        <v>756</v>
       </c>
       <c r="F119" s="4" t="s">
-        <v>770</v>
+        <v>757</v>
       </c>
       <c r="G119" s="4" t="s">
-        <v>771</v>
+        <v>758</v>
       </c>
       <c r="H119" s="4" t="s">
         <v>71</v>
       </c>
       <c r="I119" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="J119" s="4"/>
       <c r="K119" s="4" t="b">
@@ -17180,7 +17180,7 @@
       <c r="AN119" s="4"/>
       <c r="AO119" s="4"/>
       <c r="AP119" s="4" t="s">
-        <v>772</v>
+        <v>759</v>
       </c>
       <c r="AQ119" s="4"/>
       <c r="AR119" s="4"/>
@@ -17195,31 +17195,31 @@
     </row>
     <row r="120" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="4" t="s">
-        <v>773</v>
+        <v>760</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>774</v>
+        <v>761</v>
       </c>
       <c r="C120" s="4">
         <v>119</v>
       </c>
       <c r="D120" t="s">
-        <v>1033</v>
+        <v>1018</v>
       </c>
       <c r="F120" s="4" t="s">
-        <v>775</v>
+        <v>762</v>
       </c>
       <c r="G120" s="20" t="s">
-        <v>776</v>
+        <v>763</v>
       </c>
       <c r="H120" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I120" s="4" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="J120" s="4" t="s">
-        <v>737</v>
+        <v>724</v>
       </c>
       <c r="K120" s="4"/>
       <c r="L120" s="4"/>
@@ -17255,7 +17255,7 @@
         <v>0</v>
       </c>
       <c r="AF120" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AG120" s="4"/>
       <c r="AH120" s="4"/>
@@ -17270,7 +17270,7 @@
       <c r="AN120" s="4"/>
       <c r="AO120" s="4"/>
       <c r="AP120" s="4" t="s">
-        <v>777</v>
+        <v>764</v>
       </c>
       <c r="AQ120" s="4"/>
       <c r="AR120" s="4" t="s">
@@ -17289,25 +17289,25 @@
     </row>
     <row r="121" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="4" t="s">
-        <v>778</v>
+        <v>765</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>779</v>
+        <v>766</v>
       </c>
       <c r="C121" s="4">
         <v>120</v>
       </c>
       <c r="D121" t="s">
-        <v>1005</v>
+        <v>990</v>
       </c>
       <c r="E121" t="s">
-        <v>780</v>
+        <v>767</v>
       </c>
       <c r="F121" s="4" t="s">
-        <v>781</v>
+        <v>768</v>
       </c>
       <c r="G121" s="4" t="s">
-        <v>782</v>
+        <v>769</v>
       </c>
       <c r="H121" s="4" t="s">
         <v>71</v>
@@ -17316,7 +17316,7 @@
         <v>129</v>
       </c>
       <c r="J121" s="4" t="s">
-        <v>783</v>
+        <v>770</v>
       </c>
       <c r="K121" s="4" t="b">
         <v>1</v>
@@ -17374,7 +17374,7 @@
       <c r="AN121" s="4"/>
       <c r="AO121" s="4"/>
       <c r="AP121" s="4" t="s">
-        <v>784</v>
+        <v>771</v>
       </c>
       <c r="AQ121" s="4"/>
       <c r="AR121" s="4"/>
@@ -17393,25 +17393,25 @@
     </row>
     <row r="122" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="4" t="s">
-        <v>785</v>
+        <v>772</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>786</v>
+        <v>773</v>
       </c>
       <c r="C122" s="4">
         <v>121</v>
       </c>
       <c r="D122" t="s">
-        <v>1034</v>
+        <v>1019</v>
       </c>
       <c r="F122" s="4" t="s">
-        <v>787</v>
+        <v>774</v>
       </c>
       <c r="G122" s="20" t="s">
-        <v>788</v>
+        <v>775</v>
       </c>
       <c r="H122" s="4" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="I122" s="4"/>
       <c r="J122" s="4"/>
@@ -17466,7 +17466,7 @@
       <c r="AN122" s="4"/>
       <c r="AO122" s="4"/>
       <c r="AP122" s="4" t="s">
-        <v>789</v>
+        <v>776</v>
       </c>
       <c r="AQ122" s="4"/>
       <c r="AR122" s="4"/>
@@ -17483,34 +17483,34 @@
     </row>
     <row r="123" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="4" t="s">
-        <v>790</v>
+        <v>777</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>791</v>
+        <v>778</v>
       </c>
       <c r="C123" s="4">
         <v>122</v>
       </c>
       <c r="D123" t="s">
-        <v>982</v>
+        <v>967</v>
       </c>
       <c r="E123" t="s">
-        <v>792</v>
+        <v>779</v>
       </c>
       <c r="F123" s="4" t="s">
-        <v>793</v>
+        <v>780</v>
       </c>
       <c r="G123" s="4" t="s">
-        <v>794</v>
+        <v>781</v>
       </c>
       <c r="H123" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="I123" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="J123" s="4" t="s">
         <v>213</v>
-      </c>
-      <c r="I123" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="J123" s="4" t="s">
-        <v>215</v>
       </c>
       <c r="K123" s="4"/>
       <c r="L123" s="4"/>
@@ -17564,7 +17564,7 @@
       <c r="AN123" s="4"/>
       <c r="AO123" s="4"/>
       <c r="AP123" s="4" t="s">
-        <v>795</v>
+        <v>782</v>
       </c>
       <c r="AQ123" s="4"/>
       <c r="AR123" s="4"/>
@@ -17579,31 +17579,31 @@
     </row>
     <row r="124" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="4" t="s">
-        <v>796</v>
+        <v>783</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>797</v>
+        <v>784</v>
       </c>
       <c r="C124" s="4">
         <v>123</v>
       </c>
       <c r="D124" t="s">
-        <v>1006</v>
+        <v>991</v>
       </c>
       <c r="F124" s="4" t="s">
-        <v>798</v>
+        <v>785</v>
       </c>
       <c r="G124" s="4" t="s">
-        <v>799</v>
+        <v>786</v>
       </c>
       <c r="H124" s="4" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I124" s="4" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="J124" s="4" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="K124" s="4"/>
       <c r="L124" s="4"/>
@@ -17655,7 +17655,7 @@
       <c r="AN124" s="4"/>
       <c r="AO124" s="4"/>
       <c r="AP124" s="4" t="s">
-        <v>800</v>
+        <v>787</v>
       </c>
       <c r="AQ124" s="4"/>
       <c r="AR124" s="4"/>
@@ -17670,34 +17670,34 @@
     </row>
     <row r="125" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="4" t="s">
-        <v>801</v>
+        <v>788</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>802</v>
+        <v>789</v>
       </c>
       <c r="C125" s="4">
         <v>124</v>
       </c>
       <c r="D125" t="s">
-        <v>1006</v>
+        <v>991</v>
       </c>
       <c r="E125" t="s">
-        <v>803</v>
+        <v>790</v>
       </c>
       <c r="F125" s="4" t="s">
-        <v>804</v>
+        <v>791</v>
       </c>
       <c r="G125" s="4" t="s">
-        <v>805</v>
+        <v>792</v>
       </c>
       <c r="H125" s="4" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I125" s="4" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="J125" s="4" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="K125" s="4"/>
       <c r="L125" s="4"/>
@@ -17749,7 +17749,7 @@
       <c r="AN125" s="4"/>
       <c r="AO125" s="4"/>
       <c r="AP125" s="4" t="s">
-        <v>806</v>
+        <v>793</v>
       </c>
       <c r="AQ125" s="4"/>
       <c r="AR125" s="4"/>
@@ -17764,34 +17764,34 @@
     </row>
     <row r="126" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="4" t="s">
-        <v>807</v>
+        <v>794</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>808</v>
+        <v>795</v>
       </c>
       <c r="C126" s="4">
         <v>125</v>
       </c>
       <c r="D126" t="s">
-        <v>1007</v>
+        <v>992</v>
       </c>
       <c r="E126" t="s">
-        <v>1043</v>
+        <v>1028</v>
       </c>
       <c r="F126" s="4" t="s">
-        <v>809</v>
+        <v>796</v>
       </c>
       <c r="G126" s="4" t="s">
-        <v>810</v>
+        <v>797</v>
       </c>
       <c r="H126" s="4" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I126" s="4" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="J126" s="4" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="K126" s="4"/>
       <c r="L126" s="4"/>
@@ -17847,7 +17847,7 @@
       <c r="AN126" s="4"/>
       <c r="AO126" s="4"/>
       <c r="AP126" s="4" t="s">
-        <v>811</v>
+        <v>798</v>
       </c>
       <c r="AQ126" s="4"/>
       <c r="AR126" s="4"/>
@@ -17866,31 +17866,31 @@
     </row>
     <row r="127" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="4" t="s">
-        <v>812</v>
+        <v>799</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>813</v>
+        <v>800</v>
       </c>
       <c r="C127" s="4">
         <v>126</v>
       </c>
       <c r="D127" t="s">
-        <v>1008</v>
+        <v>993</v>
       </c>
       <c r="F127" s="4" t="s">
-        <v>814</v>
+        <v>801</v>
       </c>
       <c r="G127" s="4" t="s">
-        <v>815</v>
+        <v>802</v>
       </c>
       <c r="H127" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I127" s="4" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="J127" s="4" t="s">
-        <v>816</v>
+        <v>803</v>
       </c>
       <c r="K127" s="4"/>
       <c r="L127" s="4"/>
@@ -17927,7 +17927,7 @@
         <v>0</v>
       </c>
       <c r="AF127" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AG127" s="4">
         <v>5.0000000000000001E-4</v>
@@ -17948,7 +17948,7 @@
       <c r="AN127" s="4"/>
       <c r="AO127" s="4"/>
       <c r="AP127" s="4" t="s">
-        <v>817</v>
+        <v>804</v>
       </c>
       <c r="AQ127" s="4"/>
       <c r="AR127" s="4" t="s">
@@ -17969,25 +17969,25 @@
     </row>
     <row r="128" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="4" t="s">
-        <v>818</v>
+        <v>805</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>818</v>
+        <v>805</v>
       </c>
       <c r="C128" s="4">
         <v>127</v>
       </c>
       <c r="D128" t="s">
-        <v>1009</v>
+        <v>994</v>
       </c>
       <c r="E128" t="s">
-        <v>819</v>
+        <v>806</v>
       </c>
       <c r="F128" s="4" t="s">
-        <v>820</v>
+        <v>807</v>
       </c>
       <c r="G128" s="4" t="s">
-        <v>821</v>
+        <v>808</v>
       </c>
       <c r="H128" s="4" t="s">
         <v>71</v>
@@ -17996,7 +17996,7 @@
         <v>129</v>
       </c>
       <c r="J128" s="4" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="K128" s="4" t="b">
         <v>1</v>
@@ -18058,7 +18058,7 @@
       <c r="AN128" s="4"/>
       <c r="AO128" s="4"/>
       <c r="AP128" s="4" t="s">
-        <v>822</v>
+        <v>809</v>
       </c>
       <c r="AQ128" s="4"/>
       <c r="AR128" s="4"/>
@@ -18079,21 +18079,21 @@
     </row>
     <row r="129" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="4" t="s">
-        <v>823</v>
+        <v>810</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>824</v>
+        <v>811</v>
       </c>
       <c r="C129" s="4">
         <v>128</v>
       </c>
       <c r="D129" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="F129" s="4"/>
       <c r="G129" s="4"/>
       <c r="H129" s="4" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="I129" s="4"/>
       <c r="J129" s="4"/>
@@ -18104,19 +18104,19 @@
       <c r="O129" s="4"/>
       <c r="P129" s="4"/>
       <c r="Q129" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="R129" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="S129" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="T129" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="U129" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="V129" s="4"/>
       <c r="W129" s="4"/>
@@ -18128,10 +18128,10 @@
       <c r="AC129" s="4"/>
       <c r="AD129" s="4"/>
       <c r="AE129" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AF129" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AG129" s="4"/>
       <c r="AH129" s="4"/>
@@ -18146,7 +18146,7 @@
       <c r="AN129" s="4"/>
       <c r="AO129" s="4"/>
       <c r="AP129" s="4" t="s">
-        <v>825</v>
+        <v>812</v>
       </c>
       <c r="AQ129" s="4"/>
       <c r="AR129" s="4"/>
@@ -18163,21 +18163,21 @@
     </row>
     <row r="130" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="4" t="s">
-        <v>826</v>
+        <v>813</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>827</v>
+        <v>814</v>
       </c>
       <c r="C130" s="4">
         <v>129</v>
       </c>
       <c r="D130" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="F130" s="4"/>
       <c r="G130" s="4"/>
       <c r="H130" s="4" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="I130" s="4"/>
       <c r="J130" s="4"/>
@@ -18188,19 +18188,19 @@
       <c r="O130" s="4"/>
       <c r="P130" s="4"/>
       <c r="Q130" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="R130" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="S130" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="T130" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="U130" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="V130" s="4"/>
       <c r="W130" s="4"/>
@@ -18212,10 +18212,10 @@
       <c r="AC130" s="4"/>
       <c r="AD130" s="4"/>
       <c r="AE130" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AF130" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AG130" s="4"/>
       <c r="AH130" s="4"/>
@@ -18230,7 +18230,7 @@
       <c r="AN130" s="4"/>
       <c r="AO130" s="4"/>
       <c r="AP130" s="4" t="s">
-        <v>828</v>
+        <v>815</v>
       </c>
       <c r="AQ130" s="4"/>
       <c r="AR130" s="4"/>
@@ -18242,32 +18242,32 @@
       </c>
       <c r="AW130" s="4"/>
       <c r="AX130" s="22" t="s">
-        <v>829</v>
+        <v>816</v>
       </c>
     </row>
     <row r="131" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="4" t="s">
-        <v>830</v>
+        <v>817</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>831</v>
+        <v>818</v>
       </c>
       <c r="C131" s="4">
         <v>130</v>
       </c>
       <c r="D131" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="E131" t="s">
-        <v>1044</v>
+        <v>1029</v>
       </c>
       <c r="F131" s="4"/>
       <c r="G131" s="4"/>
       <c r="H131" s="4" t="s">
-        <v>832</v>
+        <v>819</v>
       </c>
       <c r="I131" s="4" t="s">
-        <v>833</v>
+        <v>820</v>
       </c>
       <c r="J131" s="4"/>
       <c r="K131" s="4"/>
@@ -18279,19 +18279,19 @@
       <c r="O131" s="4"/>
       <c r="P131" s="4"/>
       <c r="Q131" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="R131" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="S131" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="T131" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="U131" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="V131" s="4"/>
       <c r="W131" s="4"/>
@@ -18313,7 +18313,7 @@
         <v>0.06</v>
       </c>
       <c r="AI131" s="4" t="s">
-        <v>834</v>
+        <v>821</v>
       </c>
       <c r="AJ131" s="4"/>
       <c r="AK131" s="4"/>
@@ -18325,7 +18325,7 @@
       <c r="AN131" s="4"/>
       <c r="AO131" s="4"/>
       <c r="AP131" s="4" t="s">
-        <v>835</v>
+        <v>822</v>
       </c>
       <c r="AQ131" s="4"/>
       <c r="AR131" s="4"/>
@@ -18342,31 +18342,31 @@
     </row>
     <row r="132" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="4" t="s">
-        <v>836</v>
+        <v>823</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>837</v>
+        <v>824</v>
       </c>
       <c r="C132" s="4">
         <v>131</v>
       </c>
       <c r="D132" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="E132" t="s">
-        <v>838</v>
+        <v>825</v>
       </c>
       <c r="F132" s="4" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="G132" s="4" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="H132" s="4" t="s">
-        <v>832</v>
+        <v>819</v>
       </c>
       <c r="I132" s="4" t="s">
-        <v>839</v>
+        <v>826</v>
       </c>
       <c r="J132" s="4"/>
       <c r="K132" s="4"/>
@@ -18378,19 +18378,19 @@
       <c r="O132" s="4"/>
       <c r="P132" s="4"/>
       <c r="Q132" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="R132" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="S132" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="T132" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="U132" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="V132" s="4"/>
       <c r="W132" s="4"/>
@@ -18406,7 +18406,7 @@
         <v>1</v>
       </c>
       <c r="AF132" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AG132" s="4"/>
       <c r="AH132" s="4"/>
@@ -18421,7 +18421,7 @@
       <c r="AN132" s="4"/>
       <c r="AO132" s="4"/>
       <c r="AP132" s="4" t="s">
-        <v>840</v>
+        <v>827</v>
       </c>
       <c r="AQ132" s="4"/>
       <c r="AR132" s="4"/>
@@ -18442,27 +18442,27 @@
     </row>
     <row r="133" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="4" t="s">
-        <v>841</v>
+        <v>828</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>842</v>
+        <v>829</v>
       </c>
       <c r="C133" s="4">
         <v>132</v>
       </c>
       <c r="D133" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="E133" t="s">
-        <v>1045</v>
+        <v>1030</v>
       </c>
       <c r="F133" s="4"/>
       <c r="G133" s="4"/>
       <c r="H133" s="4" t="s">
-        <v>832</v>
+        <v>819</v>
       </c>
       <c r="I133" s="4" t="s">
-        <v>839</v>
+        <v>826</v>
       </c>
       <c r="J133" s="4"/>
       <c r="K133" s="4"/>
@@ -18472,19 +18472,19 @@
       <c r="O133" s="4"/>
       <c r="P133" s="4"/>
       <c r="Q133" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="R133" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="S133" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="T133" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="U133" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="V133" s="4"/>
       <c r="W133" s="4"/>
@@ -18496,10 +18496,10 @@
       <c r="AC133" s="4"/>
       <c r="AD133" s="4"/>
       <c r="AE133" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AF133" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AG133" s="4"/>
       <c r="AH133" s="4"/>
@@ -18527,31 +18527,31 @@
     </row>
     <row r="134" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="4" t="s">
-        <v>843</v>
+        <v>830</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>844</v>
+        <v>831</v>
       </c>
       <c r="C134" s="4">
         <v>133</v>
       </c>
       <c r="D134" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="E134" t="s">
-        <v>1046</v>
+        <v>1031</v>
       </c>
       <c r="F134" s="4" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="G134" s="4" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="H134" s="4" t="s">
-        <v>832</v>
+        <v>819</v>
       </c>
       <c r="I134" s="4" t="s">
-        <v>839</v>
+        <v>826</v>
       </c>
       <c r="J134" s="4"/>
       <c r="K134" s="4"/>
@@ -18563,19 +18563,19 @@
       <c r="O134" s="4"/>
       <c r="P134" s="4"/>
       <c r="Q134" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="R134" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="S134" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="T134" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="U134" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="V134" s="4"/>
       <c r="W134" s="4"/>
@@ -18587,10 +18587,10 @@
       <c r="AC134" s="4"/>
       <c r="AD134" s="4"/>
       <c r="AE134" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AF134" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AG134" s="4"/>
       <c r="AH134" s="4"/>
@@ -18605,7 +18605,7 @@
       <c r="AN134" s="4"/>
       <c r="AO134" s="4"/>
       <c r="AP134" s="4" t="s">
-        <v>845</v>
+        <v>832</v>
       </c>
       <c r="AQ134" s="4"/>
       <c r="AR134" s="4"/>
@@ -18626,31 +18626,31 @@
     </row>
     <row r="135" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="4" t="s">
-        <v>846</v>
+        <v>833</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>847</v>
+        <v>834</v>
       </c>
       <c r="C135" s="4">
         <v>134</v>
       </c>
       <c r="D135" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="E135" t="s">
-        <v>848</v>
+        <v>1059</v>
       </c>
       <c r="F135" s="4" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="G135" s="4" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="H135" s="4" t="s">
-        <v>832</v>
+        <v>819</v>
       </c>
       <c r="I135" s="4" t="s">
-        <v>839</v>
+        <v>826</v>
       </c>
       <c r="J135" s="4"/>
       <c r="K135" s="4"/>
@@ -18662,19 +18662,19 @@
       <c r="O135" s="4"/>
       <c r="P135" s="4"/>
       <c r="Q135" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="R135" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="S135" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="T135" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="U135" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="V135" s="4"/>
       <c r="W135" s="4"/>
@@ -18686,10 +18686,10 @@
       <c r="AC135" s="4"/>
       <c r="AD135" s="4"/>
       <c r="AE135" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AF135" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AG135" s="4"/>
       <c r="AH135" s="4"/>
@@ -18704,7 +18704,7 @@
       <c r="AN135" s="4"/>
       <c r="AO135" s="4"/>
       <c r="AP135" s="4" t="s">
-        <v>845</v>
+        <v>832</v>
       </c>
       <c r="AQ135" s="4"/>
       <c r="AR135" s="4"/>
@@ -18719,31 +18719,31 @@
     </row>
     <row r="136" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="4" t="s">
-        <v>849</v>
+        <v>835</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>850</v>
+        <v>836</v>
       </c>
       <c r="C136" s="4">
         <v>135</v>
       </c>
       <c r="D136" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="E136" t="s">
-        <v>1047</v>
+        <v>1032</v>
       </c>
       <c r="F136" s="4" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="G136" s="4" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="H136" s="4" t="s">
-        <v>832</v>
+        <v>819</v>
       </c>
       <c r="I136" s="4" t="s">
-        <v>839</v>
+        <v>826</v>
       </c>
       <c r="J136" s="4"/>
       <c r="K136" s="4"/>
@@ -18753,19 +18753,19 @@
       <c r="O136" s="4"/>
       <c r="P136" s="4"/>
       <c r="Q136" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="R136" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="S136" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="T136" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="U136" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="V136" s="4"/>
       <c r="W136" s="4"/>
@@ -18777,10 +18777,10 @@
       <c r="AC136" s="4"/>
       <c r="AD136" s="4"/>
       <c r="AE136" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AF136" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AG136" s="4"/>
       <c r="AH136" s="4"/>
@@ -18795,7 +18795,7 @@
       <c r="AN136" s="4"/>
       <c r="AO136" s="4"/>
       <c r="AP136" s="4" t="s">
-        <v>845</v>
+        <v>832</v>
       </c>
       <c r="AQ136" s="4"/>
       <c r="AR136" s="4"/>
@@ -18816,31 +18816,31 @@
     </row>
     <row r="137" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="4" t="s">
-        <v>851</v>
+        <v>837</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>852</v>
+        <v>838</v>
       </c>
       <c r="C137" s="4">
         <v>136</v>
       </c>
       <c r="D137" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="E137" t="s">
-        <v>1048</v>
+        <v>1033</v>
       </c>
       <c r="F137" s="4" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="G137" s="4" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="H137" s="4" t="s">
-        <v>832</v>
+        <v>819</v>
       </c>
       <c r="I137" s="4" t="s">
-        <v>839</v>
+        <v>826</v>
       </c>
       <c r="J137" s="4"/>
       <c r="K137" s="4"/>
@@ -18850,19 +18850,19 @@
       <c r="O137" s="4"/>
       <c r="P137" s="4"/>
       <c r="Q137" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="R137" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="S137" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="T137" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="U137" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="V137" s="4"/>
       <c r="W137" s="4"/>
@@ -18874,10 +18874,10 @@
       <c r="AC137" s="4"/>
       <c r="AD137" s="4"/>
       <c r="AE137" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AF137" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AG137" s="4"/>
       <c r="AH137" s="4"/>
@@ -18892,7 +18892,7 @@
       <c r="AN137" s="4"/>
       <c r="AO137" s="4"/>
       <c r="AP137" s="4" t="s">
-        <v>845</v>
+        <v>832</v>
       </c>
       <c r="AQ137" s="4"/>
       <c r="AR137" s="4"/>
@@ -18913,31 +18913,31 @@
     </row>
     <row r="138" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="4" t="s">
-        <v>853</v>
+        <v>839</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>854</v>
+        <v>840</v>
       </c>
       <c r="C138" s="4">
         <v>137</v>
       </c>
       <c r="D138" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="E138" t="s">
-        <v>855</v>
+        <v>841</v>
       </c>
       <c r="F138" s="4" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="G138" s="4" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="H138" s="4" t="s">
-        <v>832</v>
+        <v>819</v>
       </c>
       <c r="I138" s="4" t="s">
-        <v>839</v>
+        <v>826</v>
       </c>
       <c r="J138" s="4"/>
       <c r="K138" s="4"/>
@@ -18947,19 +18947,19 @@
       <c r="O138" s="4"/>
       <c r="P138" s="4"/>
       <c r="Q138" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="R138" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="S138" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="T138" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="U138" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="V138" s="4"/>
       <c r="W138" s="4"/>
@@ -18971,10 +18971,10 @@
       <c r="AC138" s="4"/>
       <c r="AD138" s="4"/>
       <c r="AE138" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AF138" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AG138" s="4"/>
       <c r="AH138" s="4"/>
@@ -18989,7 +18989,7 @@
       <c r="AN138" s="4"/>
       <c r="AO138" s="4"/>
       <c r="AP138" s="4" t="s">
-        <v>845</v>
+        <v>832</v>
       </c>
       <c r="AQ138" s="4"/>
       <c r="AR138" s="4"/>
@@ -19004,31 +19004,31 @@
     </row>
     <row r="139" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="4" t="s">
-        <v>856</v>
+        <v>842</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>857</v>
+        <v>843</v>
       </c>
       <c r="C139" s="4">
         <v>138</v>
       </c>
       <c r="D139" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="E139" t="s">
-        <v>858</v>
+        <v>844</v>
       </c>
       <c r="F139" s="4" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="G139" s="4" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="H139" s="4" t="s">
-        <v>832</v>
+        <v>819</v>
       </c>
       <c r="I139" s="4" t="s">
-        <v>833</v>
+        <v>820</v>
       </c>
       <c r="J139" s="4"/>
       <c r="K139" s="4"/>
@@ -19049,10 +19049,10 @@
         <v>0</v>
       </c>
       <c r="T139" s="27" t="s">
-        <v>1037</v>
+        <v>1022</v>
       </c>
       <c r="U139" s="27" t="s">
-        <v>1037</v>
+        <v>1022</v>
       </c>
       <c r="V139" s="4"/>
       <c r="W139" s="4"/>
@@ -19074,7 +19074,7 @@
         <v>0.08</v>
       </c>
       <c r="AI139" s="4" t="s">
-        <v>834</v>
+        <v>821</v>
       </c>
       <c r="AJ139" s="4"/>
       <c r="AK139" s="4"/>
@@ -19088,7 +19088,7 @@
       <c r="AN139" s="4"/>
       <c r="AO139" s="4"/>
       <c r="AP139" s="4" t="s">
-        <v>859</v>
+        <v>845</v>
       </c>
       <c r="AQ139" s="4"/>
       <c r="AR139" s="4"/>
@@ -19109,27 +19109,27 @@
     </row>
     <row r="140" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="4" t="s">
-        <v>860</v>
+        <v>846</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>861</v>
+        <v>847</v>
       </c>
       <c r="C140" s="4">
         <v>139</v>
       </c>
       <c r="D140" t="s">
-        <v>1035</v>
+        <v>1020</v>
       </c>
       <c r="F140" s="4"/>
       <c r="G140" s="4"/>
       <c r="H140" s="4" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I140" s="4" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="J140" s="4" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="K140" s="4"/>
       <c r="L140" s="4"/>
@@ -19182,7 +19182,7 @@
       <c r="AN140" s="4"/>
       <c r="AO140" s="4"/>
       <c r="AP140" s="4" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="AQ140" s="4"/>
       <c r="AR140" s="4"/>
@@ -19197,22 +19197,22 @@
     </row>
     <row r="141" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="4" t="s">
-        <v>862</v>
+        <v>848</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>863</v>
+        <v>849</v>
       </c>
       <c r="C141" s="4">
         <v>140</v>
       </c>
       <c r="D141" t="s">
-        <v>1010</v>
+        <v>995</v>
       </c>
       <c r="F141" s="4" t="s">
-        <v>864</v>
+        <v>850</v>
       </c>
       <c r="G141" s="4" t="s">
-        <v>865</v>
+        <v>851</v>
       </c>
       <c r="H141" s="4" t="s">
         <v>71</v>
@@ -19275,7 +19275,7 @@
       <c r="AN141" s="4"/>
       <c r="AO141" s="4"/>
       <c r="AP141" s="4" t="s">
-        <v>866</v>
+        <v>852</v>
       </c>
       <c r="AQ141" s="4"/>
       <c r="AR141" s="4"/>
@@ -19290,22 +19290,22 @@
     </row>
     <row r="142" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="4" t="s">
-        <v>867</v>
+        <v>853</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>868</v>
+        <v>854</v>
       </c>
       <c r="C142" s="4">
         <v>141</v>
       </c>
       <c r="D142" t="s">
-        <v>1010</v>
+        <v>995</v>
       </c>
       <c r="F142" s="4" t="s">
-        <v>869</v>
+        <v>855</v>
       </c>
       <c r="G142" s="4" t="s">
-        <v>870</v>
+        <v>856</v>
       </c>
       <c r="H142" s="4" t="s">
         <v>71</v>
@@ -19372,7 +19372,7 @@
       <c r="AN142" s="4"/>
       <c r="AO142" s="4"/>
       <c r="AP142" s="4" t="s">
-        <v>871</v>
+        <v>857</v>
       </c>
       <c r="AQ142" s="4"/>
       <c r="AR142" s="4"/>
@@ -19391,34 +19391,34 @@
     </row>
     <row r="143" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" s="4" t="s">
-        <v>872</v>
+        <v>858</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>873</v>
+        <v>859</v>
       </c>
       <c r="C143" s="4">
         <v>142</v>
       </c>
       <c r="D143" t="s">
-        <v>1011</v>
+        <v>996</v>
       </c>
       <c r="E143" t="s">
-        <v>874</v>
+        <v>860</v>
       </c>
       <c r="F143" s="4" t="s">
-        <v>875</v>
+        <v>861</v>
       </c>
       <c r="G143" s="4" t="s">
-        <v>876</v>
+        <v>862</v>
       </c>
       <c r="H143" s="4" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I143" s="4" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="J143" s="4" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="K143" s="4"/>
       <c r="L143" s="4"/>
@@ -19464,7 +19464,7 @@
         <v>0.2</v>
       </c>
       <c r="AI143" s="4" t="s">
-        <v>877</v>
+        <v>863</v>
       </c>
       <c r="AJ143" s="4"/>
       <c r="AK143" s="4"/>
@@ -19478,7 +19478,7 @@
       </c>
       <c r="AO143" s="4"/>
       <c r="AP143" s="4" t="s">
-        <v>878</v>
+        <v>864</v>
       </c>
       <c r="AQ143" s="4"/>
       <c r="AR143" s="4"/>
@@ -19497,34 +19497,34 @@
     </row>
     <row r="144" spans="1:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="4" t="s">
-        <v>879</v>
+        <v>865</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>880</v>
+        <v>866</v>
       </c>
       <c r="C144" s="4">
         <v>143</v>
       </c>
       <c r="D144" t="s">
-        <v>1011</v>
+        <v>996</v>
       </c>
       <c r="E144" t="s">
-        <v>881</v>
+        <v>867</v>
       </c>
       <c r="F144" s="4" t="s">
-        <v>882</v>
+        <v>868</v>
       </c>
       <c r="G144" s="4" t="s">
-        <v>883</v>
+        <v>869</v>
       </c>
       <c r="H144" s="4" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I144" s="4" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="J144" s="4" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="K144" s="4"/>
       <c r="L144" s="4"/>
@@ -19580,7 +19580,7 @@
       <c r="AN144" s="4"/>
       <c r="AO144" s="4"/>
       <c r="AP144" s="4" t="s">
-        <v>884</v>
+        <v>870</v>
       </c>
       <c r="AQ144" s="4"/>
       <c r="AR144" s="4"/>
@@ -19599,34 +19599,34 @@
     </row>
     <row r="145" spans="1:51" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="4" t="s">
-        <v>885</v>
+        <v>871</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>886</v>
+        <v>872</v>
       </c>
       <c r="C145" s="4">
         <v>144</v>
       </c>
       <c r="D145" t="s">
-        <v>1012</v>
+        <v>997</v>
       </c>
       <c r="E145" t="s">
-        <v>887</v>
+        <v>873</v>
       </c>
       <c r="F145" s="4" t="s">
-        <v>888</v>
+        <v>874</v>
       </c>
       <c r="G145" s="4" t="s">
-        <v>889</v>
+        <v>875</v>
       </c>
       <c r="H145" s="4" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I145" s="4" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="J145" s="4" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="K145" s="4"/>
       <c r="L145" s="4"/>
@@ -19682,7 +19682,7 @@
       <c r="AN145" s="4"/>
       <c r="AO145" s="4"/>
       <c r="AP145" s="4" t="s">
-        <v>890</v>
+        <v>876</v>
       </c>
       <c r="AQ145" s="4"/>
       <c r="AR145" s="4"/>
@@ -19699,34 +19699,34 @@
     </row>
     <row r="146" spans="1:51" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="4" t="s">
-        <v>891</v>
+        <v>877</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>892</v>
+        <v>878</v>
       </c>
       <c r="C146" s="4">
         <v>145</v>
       </c>
       <c r="D146" t="s">
-        <v>1013</v>
+        <v>998</v>
       </c>
       <c r="E146" t="s">
-        <v>893</v>
+        <v>879</v>
       </c>
       <c r="F146" s="4" t="s">
-        <v>894</v>
+        <v>880</v>
       </c>
       <c r="G146" s="4" t="s">
-        <v>895</v>
+        <v>881</v>
       </c>
       <c r="H146" s="4" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I146" s="4" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="J146" s="4" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="K146" s="4"/>
       <c r="L146" s="4"/>
@@ -19780,7 +19780,7 @@
       </c>
       <c r="AO146" s="4"/>
       <c r="AP146" s="4" t="s">
-        <v>896</v>
+        <v>1073</v>
       </c>
       <c r="AQ146" s="4"/>
       <c r="AR146" s="4"/>
@@ -19795,34 +19795,34 @@
     </row>
     <row r="147" spans="1:51" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="4" t="s">
-        <v>897</v>
+        <v>882</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>898</v>
+        <v>883</v>
       </c>
       <c r="C147" s="4">
         <v>146</v>
       </c>
       <c r="D147" t="s">
-        <v>1014</v>
+        <v>999</v>
       </c>
       <c r="E147" t="s">
-        <v>899</v>
+        <v>884</v>
       </c>
       <c r="F147" s="4" t="s">
-        <v>900</v>
+        <v>885</v>
       </c>
       <c r="G147" s="4" t="s">
-        <v>901</v>
+        <v>886</v>
       </c>
       <c r="H147" s="4" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I147" s="4" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="J147" s="4" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="K147" s="4"/>
       <c r="L147" s="4"/>
@@ -19876,7 +19876,7 @@
       <c r="AN147" s="4"/>
       <c r="AO147" s="4"/>
       <c r="AP147" s="4" t="s">
-        <v>902</v>
+        <v>887</v>
       </c>
       <c r="AQ147" s="4"/>
       <c r="AR147" s="4"/>
@@ -19891,25 +19891,25 @@
     </row>
     <row r="148" spans="1:51" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="4" t="s">
-        <v>903</v>
+        <v>888</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>904</v>
+        <v>889</v>
       </c>
       <c r="C148" s="4">
         <v>147</v>
       </c>
       <c r="D148" t="s">
-        <v>1002</v>
+        <v>987</v>
       </c>
       <c r="E148" t="s">
-        <v>905</v>
+        <v>890</v>
       </c>
       <c r="F148" s="4" t="s">
-        <v>906</v>
+        <v>891</v>
       </c>
       <c r="G148" s="4" t="s">
-        <v>907</v>
+        <v>892</v>
       </c>
       <c r="H148" s="4" t="s">
         <v>71</v>
@@ -19918,7 +19918,7 @@
         <v>129</v>
       </c>
       <c r="J148" s="4" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="K148" s="4" t="b">
         <v>1</v>
@@ -19976,7 +19976,7 @@
       <c r="AN148" s="4"/>
       <c r="AO148" s="4"/>
       <c r="AP148" s="4" t="s">
-        <v>908</v>
+        <v>893</v>
       </c>
       <c r="AQ148" s="4"/>
       <c r="AR148" s="4"/>
@@ -19995,25 +19995,25 @@
     </row>
     <row r="149" spans="1:51" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="4" t="s">
-        <v>909</v>
+        <v>894</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>910</v>
+        <v>895</v>
       </c>
       <c r="C149" s="4">
         <v>148</v>
       </c>
       <c r="D149" t="s">
-        <v>1002</v>
+        <v>987</v>
       </c>
       <c r="E149" t="s">
-        <v>911</v>
+        <v>896</v>
       </c>
       <c r="F149" s="4" t="s">
-        <v>912</v>
+        <v>897</v>
       </c>
       <c r="G149" s="4" t="s">
-        <v>913</v>
+        <v>898</v>
       </c>
       <c r="H149" s="4" t="s">
         <v>71</v>
@@ -20022,7 +20022,7 @@
         <v>129</v>
       </c>
       <c r="J149" s="4" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="K149" s="4" t="b">
         <v>1</v>
@@ -20078,7 +20078,7 @@
       <c r="AN149" s="4"/>
       <c r="AO149" s="4"/>
       <c r="AP149" s="4" t="s">
-        <v>914</v>
+        <v>899</v>
       </c>
       <c r="AQ149" s="4"/>
       <c r="AR149" s="4"/>
@@ -20097,21 +20097,21 @@
     </row>
     <row r="150" spans="1:51" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="4" t="s">
-        <v>915</v>
+        <v>900</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
       <c r="C150" s="4">
         <v>149</v>
       </c>
       <c r="D150" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="F150" s="4"/>
       <c r="G150" s="4"/>
       <c r="H150" s="4" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="I150" s="4"/>
       <c r="J150" s="4"/>
@@ -20122,19 +20122,19 @@
       <c r="O150" s="4"/>
       <c r="P150" s="4"/>
       <c r="Q150" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="R150" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="S150" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="T150" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="U150" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="V150" s="4"/>
       <c r="W150" s="4"/>
@@ -20146,10 +20146,10 @@
       <c r="AC150" s="4"/>
       <c r="AD150" s="4"/>
       <c r="AE150" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AF150" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AG150" s="4"/>
       <c r="AH150" s="4"/>
@@ -20164,7 +20164,7 @@
       <c r="AN150" s="4"/>
       <c r="AO150" s="4"/>
       <c r="AP150" s="4" t="s">
-        <v>917</v>
+        <v>902</v>
       </c>
       <c r="AQ150" s="4"/>
       <c r="AR150" s="4"/>
@@ -20179,28 +20179,28 @@
     </row>
     <row r="151" spans="1:51" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="4" t="s">
-        <v>918</v>
+        <v>903</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>919</v>
+        <v>904</v>
       </c>
       <c r="C151" s="4">
         <v>150</v>
       </c>
       <c r="D151" t="s">
-        <v>984</v>
+        <v>969</v>
       </c>
       <c r="F151" s="4" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="G151" s="4" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="H151" s="4" t="s">
-        <v>832</v>
+        <v>819</v>
       </c>
       <c r="I151" s="4" t="s">
-        <v>833</v>
+        <v>820</v>
       </c>
       <c r="J151" s="4"/>
       <c r="K151" s="4"/>
@@ -20245,7 +20245,7 @@
       <c r="AG151" s="4"/>
       <c r="AH151" s="4"/>
       <c r="AI151" s="4" t="s">
-        <v>920</v>
+        <v>905</v>
       </c>
       <c r="AJ151" s="4"/>
       <c r="AK151" s="4"/>
@@ -20257,10 +20257,10 @@
       <c r="AN151" s="4"/>
       <c r="AO151" s="4"/>
       <c r="AP151" s="4" t="s">
-        <v>921</v>
+        <v>906</v>
       </c>
       <c r="AQ151" s="4" t="s">
-        <v>922</v>
+        <v>907</v>
       </c>
       <c r="AR151" s="4"/>
       <c r="AS151" s="4" t="b">
@@ -20280,25 +20280,25 @@
     </row>
     <row r="152" spans="1:51" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="4" t="s">
-        <v>923</v>
+        <v>908</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>924</v>
+        <v>909</v>
       </c>
       <c r="C152" s="4">
         <v>151</v>
       </c>
       <c r="D152" t="s">
-        <v>984</v>
+        <v>969</v>
       </c>
       <c r="E152" t="s">
-        <v>925</v>
+        <v>910</v>
       </c>
       <c r="F152" s="4" t="s">
-        <v>926</v>
+        <v>911</v>
       </c>
       <c r="G152" s="4" t="s">
-        <v>927</v>
+        <v>912</v>
       </c>
       <c r="H152" s="4" t="s">
         <v>71</v>
@@ -20307,7 +20307,7 @@
         <v>129</v>
       </c>
       <c r="J152" s="4" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="K152" s="4" t="b">
         <v>1</v>
@@ -20353,7 +20353,7 @@
       <c r="AG152" s="4"/>
       <c r="AH152" s="4"/>
       <c r="AI152" s="4" t="s">
-        <v>920</v>
+        <v>905</v>
       </c>
       <c r="AJ152" s="4"/>
       <c r="AK152" s="4"/>
@@ -20365,7 +20365,7 @@
       <c r="AN152" s="4"/>
       <c r="AO152" s="4"/>
       <c r="AP152" s="4" t="s">
-        <v>928</v>
+        <v>913</v>
       </c>
       <c r="AQ152" s="4"/>
       <c r="AR152" s="4"/>
@@ -20386,31 +20386,31 @@
     </row>
     <row r="153" spans="1:51" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="4" t="s">
-        <v>929</v>
+        <v>914</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>930</v>
+        <v>915</v>
       </c>
       <c r="C153" s="4">
         <v>152</v>
       </c>
       <c r="D153" t="s">
-        <v>984</v>
+        <v>969</v>
       </c>
       <c r="E153" t="s">
-        <v>931</v>
+        <v>916</v>
       </c>
       <c r="F153" s="4" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="G153" s="4" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="H153" s="4" t="s">
-        <v>832</v>
+        <v>819</v>
       </c>
       <c r="I153" s="4" t="s">
-        <v>833</v>
+        <v>820</v>
       </c>
       <c r="J153" s="4"/>
       <c r="K153" s="4"/>
@@ -20471,7 +20471,7 @@
       <c r="AN153" s="4"/>
       <c r="AO153" s="4"/>
       <c r="AP153" s="4" t="s">
-        <v>932</v>
+        <v>917</v>
       </c>
       <c r="AQ153" s="4"/>
       <c r="AR153" s="4"/>
@@ -56086,10 +56086,10 @@
   <sheetData>
     <row r="1" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A1" s="24" t="s">
-        <v>933</v>
+        <v>918</v>
       </c>
       <c r="B1" s="24" t="s">
-        <v>934</v>
+        <v>919</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="75" customHeight="1" x14ac:dyDescent="0.2">
@@ -56097,7 +56097,7 @@
         <v>59</v>
       </c>
       <c r="B2" s="25" t="s">
-        <v>935</v>
+        <v>920</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="75" customHeight="1" x14ac:dyDescent="0.2">
@@ -56105,7 +56105,7 @@
         <v>60</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>936</v>
+        <v>921</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="75" customHeight="1" x14ac:dyDescent="0.2">
@@ -56113,15 +56113,15 @@
         <v>61</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>937</v>
+        <v>922</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A5" s="24" t="s">
-        <v>1038</v>
+        <v>1023</v>
       </c>
       <c r="B5" s="26" t="s">
-        <v>1039</v>
+        <v>1024</v>
       </c>
     </row>
   </sheetData>
@@ -56141,33 +56141,33 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="30" t="s">
-        <v>1067</v>
+        <v>1052</v>
       </c>
       <c r="B1" s="30" t="s">
-        <v>1068</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="30" t="s">
-        <v>1069</v>
+        <v>1054</v>
       </c>
       <c r="B2" s="30" t="s">
-        <v>1073</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="30" t="s">
-        <v>1070</v>
+        <v>1055</v>
       </c>
       <c r="B3" s="30" t="s">
-        <v>1071</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="30" t="s">
-        <v>1072</v>
-      </c>
-      <c r="B4" s="37" t="s">
+        <v>1057</v>
+      </c>
+      <c r="B4" s="31" t="s">
         <v>1074</v>
       </c>
     </row>
